--- a/Deliverables/BOM/ARC_1.0.5/eSpark_BOM_ARC_1.0.5.xlsx
+++ b/Deliverables/BOM/ARC_1.0.5/eSpark_BOM_ARC_1.0.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Oliver-ARC\Deliverables\BOM\ARC_1.0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571CDA42-C9F3-492C-86C6-72FE29571EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30E3B7D-6946-4119-B9D1-278838512855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="455">
   <si>
     <t>Component list</t>
   </si>
@@ -1386,13 +1386,16 @@
     <t>Single Board Cost</t>
   </si>
   <si>
-    <t>Need Custom Supplier Quotation</t>
-  </si>
-  <si>
     <t>Bill of Materials for Project [ARC_1.0.5]</t>
   </si>
   <si>
     <t>[ARC_1.0.5]</t>
+  </si>
+  <si>
+    <t>LULU Quote</t>
+  </si>
+  <si>
+    <t>Custom Supplier</t>
   </si>
 </sst>
 </file>
@@ -1889,7 +1892,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2080,9 +2083,6 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2115,6 +2115,29 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2465,7 +2488,7 @@
     <col min="4" max="4" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="29.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -2473,7 +2496,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -2491,15 +2514,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2510,7 +2533,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2535,7 +2558,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2549,7 +2572,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="73"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2560,7 +2583,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2574,7 +2597,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="74"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2599,7 +2622,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="74"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2620,7 +2643,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="74"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2641,7 +2664,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="74"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2662,7 +2685,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="74"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2851,7 +2874,7 @@
       <c r="F12" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="46" t="s">
         <v>195</v>
       </c>
       <c r="H12" s="46" t="s">
@@ -3673,7 +3696,7 @@
       <c r="R26" s="48"/>
       <c r="S26" s="49"/>
     </row>
-    <row r="27" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="38">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -4513,7 +4536,7 @@
       <c r="R41" s="52"/>
       <c r="S41" s="52"/>
     </row>
-    <row r="42" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="38">
         <f t="shared" si="0"/>
@@ -5611,7 +5634,7 @@
       <c r="R61" s="52"/>
       <c r="S61" s="52"/>
     </row>
-    <row r="62" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="38">
         <f>ROW(B62) - ROW($B$9)</f>
@@ -6170,51 +6193,61 @@
       <c r="R71" s="52"/>
       <c r="S71" s="52"/>
     </row>
-    <row r="72" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1"/>
-      <c r="B72" s="38">
+    <row r="72" spans="1:19" s="88" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="80"/>
+      <c r="B72" s="81">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="59" t="s">
+      <c r="C72" s="82" t="s">
         <v>353</v>
       </c>
-      <c r="D72" s="46" t="s">
+      <c r="D72" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="E72" s="47" t="s">
+      <c r="E72" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="F72" s="46" t="s">
+      <c r="F72" s="83" t="s">
         <v>186</v>
       </c>
-      <c r="G72" s="47" t="s">
+      <c r="G72" s="84" t="s">
         <v>242</v>
       </c>
-      <c r="H72" s="46" t="s">
+      <c r="H72" s="83" t="s">
         <v>290</v>
       </c>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46" t="s">
-        <v>356</v>
-      </c>
-      <c r="L72" s="47">
-        <v>1</v>
-      </c>
-      <c r="M72" s="46">
+      <c r="I72" s="83" t="s">
+        <v>356</v>
+      </c>
+      <c r="J72" s="83" t="s">
+        <v>356</v>
+      </c>
+      <c r="K72" s="83" t="s">
+        <v>356</v>
+      </c>
+      <c r="L72" s="84">
+        <v>1</v>
+      </c>
+      <c r="M72" s="83">
         <f t="shared" ref="M72:M84" si="3">L72*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="46"/>
-      <c r="O72" s="64"/>
-      <c r="P72" s="53"/>
-      <c r="Q72" s="53">
+      <c r="N72" s="83">
+        <v>6</v>
+      </c>
+      <c r="O72" s="85" t="s">
+        <v>454</v>
+      </c>
+      <c r="P72" s="86">
+        <v>10.87</v>
+      </c>
+      <c r="Q72" s="86">
         <f t="shared" ref="Q72:Q84" si="4">P72*N72</f>
-        <v>0</v>
-      </c>
-      <c r="R72" s="70" t="s">
-        <v>451</v>
+        <v>65.22</v>
+      </c>
+      <c r="R72" s="87" t="s">
+        <v>453</v>
       </c>
       <c r="S72" s="49"/>
     </row>
@@ -6386,7 +6419,7 @@
       <c r="R75" s="52"/>
       <c r="S75" s="52"/>
     </row>
-    <row r="76" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="38">
         <f t="shared" si="0"/>
@@ -6410,8 +6443,12 @@
       <c r="H76" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
+      <c r="I76" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="J76" s="46" t="s">
+        <v>356</v>
+      </c>
       <c r="K76" s="46" t="s">
         <v>356</v>
       </c>
@@ -6422,15 +6459,21 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N76" s="46"/>
-      <c r="O76" s="64"/>
-      <c r="P76" s="53"/>
+      <c r="N76" s="46">
+        <v>6</v>
+      </c>
+      <c r="O76" s="64" t="s">
+        <v>454</v>
+      </c>
+      <c r="P76" s="53">
+        <v>43.5</v>
+      </c>
       <c r="Q76" s="53">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R76" s="70" t="s">
-        <v>451</v>
+        <v>261</v>
+      </c>
+      <c r="R76" s="87" t="s">
+        <v>453</v>
       </c>
       <c r="S76" s="49"/>
     </row>
@@ -6602,7 +6645,7 @@
       <c r="R79" s="52"/>
       <c r="S79" s="52"/>
     </row>
-    <row r="80" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="38">
         <f t="shared" si="0"/>
@@ -6623,9 +6666,15 @@
       <c r="G80" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
+      <c r="H80" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="I80" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="J80" s="46" t="s">
+        <v>356</v>
+      </c>
       <c r="K80" s="46" t="s">
         <v>356</v>
       </c>
@@ -6636,15 +6685,21 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N80" s="46"/>
-      <c r="O80" s="64"/>
-      <c r="P80" s="53"/>
+      <c r="N80" s="46">
+        <v>6</v>
+      </c>
+      <c r="O80" s="64" t="s">
+        <v>454</v>
+      </c>
+      <c r="P80" s="53">
+        <v>3.2</v>
+      </c>
       <c r="Q80" s="53">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R80" s="70" t="s">
-        <v>451</v>
+        <v>19.200000000000003</v>
+      </c>
+      <c r="R80" s="87" t="s">
+        <v>453</v>
       </c>
       <c r="S80" s="49"/>
     </row>
@@ -6704,7 +6759,7 @@
       <c r="R81" s="52"/>
       <c r="S81" s="52"/>
     </row>
-    <row r="82" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="38">
         <f t="shared" si="0"/>
@@ -6728,8 +6783,12 @@
       <c r="H82" s="46" t="s">
         <v>297</v>
       </c>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
+      <c r="I82" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="J82" s="46" t="s">
+        <v>356</v>
+      </c>
       <c r="K82" s="46" t="s">
         <v>356</v>
       </c>
@@ -6740,15 +6799,21 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N82" s="46"/>
-      <c r="O82" s="64"/>
-      <c r="P82" s="53"/>
+      <c r="N82" s="46">
+        <v>6</v>
+      </c>
+      <c r="O82" s="64" t="s">
+        <v>454</v>
+      </c>
+      <c r="P82" s="53">
+        <v>1.45</v>
+      </c>
       <c r="Q82" s="53">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R82" s="70" t="s">
-        <v>451</v>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R82" s="87" t="s">
+        <v>453</v>
       </c>
       <c r="S82" s="49"/>
     </row>
@@ -6878,17 +6943,17 @@
       <c r="K85" s="37"/>
       <c r="L85" s="37"/>
       <c r="M85" s="37"/>
-      <c r="N85" s="79" t="s">
+      <c r="N85" s="78" t="s">
         <v>449</v>
       </c>
-      <c r="O85" s="80"/>
-      <c r="P85" s="80"/>
+      <c r="O85" s="79"/>
+      <c r="P85" s="79"/>
       <c r="Q85" s="68">
         <f>SUM(Q10:Q84)</f>
-        <v>156.65860000000001</v>
-      </c>
-      <c r="R85" s="75"/>
-      <c r="S85" s="76"/>
+        <v>510.77860000000004</v>
+      </c>
+      <c r="R85" s="74"/>
+      <c r="S85" s="75"/>
     </row>
     <row r="86" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
@@ -6904,17 +6969,17 @@
       <c r="K86" s="10"/>
       <c r="L86" s="10"/>
       <c r="M86" s="10"/>
-      <c r="N86" s="79" t="s">
+      <c r="N86" s="78" t="s">
         <v>450</v>
       </c>
-      <c r="O86" s="80"/>
-      <c r="P86" s="80"/>
+      <c r="O86" s="79"/>
+      <c r="P86" s="79"/>
       <c r="Q86" s="69">
         <f>Q85/5</f>
-        <v>31.331720000000001</v>
-      </c>
-      <c r="R86" s="77"/>
-      <c r="S86" s="78"/>
+        <v>102.15572</v>
+      </c>
+      <c r="R86" s="76"/>
+      <c r="S86" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverables/BOM/ARC_1.0.5/eSpark_BOM_ARC_1.0.5.xlsx
+++ b/Deliverables/BOM/ARC_1.0.5/eSpark_BOM_ARC_1.0.5.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Oliver-ARC\Deliverables\BOM\ARC_1.0.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Oliver-ARC\Deliverables\BOM\ARC_1.0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30E3B7D-6946-4119-B9D1-278838512855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -60,9 +59,6 @@
     <t>C2, C33, C34</t>
   </si>
   <si>
-    <t>C3, C4, C7, C8, C13, C18, C20, C23, C24, C32, C36, C37, C38, C41, C42</t>
-  </si>
-  <si>
     <t>C5</t>
   </si>
   <si>
@@ -1396,12 +1392,15 @@
   </si>
   <si>
     <t>Custom Supplier</t>
+  </si>
+  <si>
+    <t>C3, C4, C7, C8, C13, C18, C20, C23, C24, C32, C36, C37, C38, C41, C42, C45</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -2020,22 +2019,7 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2053,9 +2037,6 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2068,13 +2049,7 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2083,6 +2058,29 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2115,29 +2113,30 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2478,7 +2477,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2514,15 +2513,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="72"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2532,8 +2531,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="55" t="s">
-        <v>451</v>
+      <c r="F2" s="50" t="s">
+        <v>450</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2557,8 +2556,8 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="56" t="s">
-        <v>452</v>
+      <c r="F3" s="51" t="s">
+        <v>451</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2572,7 +2571,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="72"/>
+      <c r="S3" s="73"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2582,8 +2581,8 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="57" t="s">
-        <v>452</v>
+      <c r="F4" s="52" t="s">
+        <v>451</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2597,7 +2596,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="73"/>
+      <c r="S4" s="74"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2607,7 +2606,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="53" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -2622,7 +2621,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="73"/>
+      <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2643,7 +2642,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="73"/>
+      <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2664,7 +2663,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="73"/>
+      <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2685,7 +2684,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="73"/>
+      <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2693,55 +2692,55 @@
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="J9" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="K9" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="K9" s="30" t="s">
+      <c r="L9" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>360</v>
       </c>
-      <c r="L9" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>361</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>362</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="R9" s="32" t="s">
+      <c r="S9" s="32" t="s">
         <v>366</v>
-      </c>
-      <c r="S9" s="32" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2750,32 +2749,32 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="59" t="s">
-        <v>342</v>
+      <c r="C10" s="54" t="s">
+        <v>341</v>
       </c>
       <c r="D10" s="46" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L10" s="47">
         <v>2</v>
@@ -2787,18 +2786,18 @@
       <c r="N10" s="46">
         <v>11</v>
       </c>
-      <c r="O10" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P10" s="53">
+      <c r="O10" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P10" s="49">
         <v>0.24690000000000001</v>
       </c>
-      <c r="Q10" s="53">
+      <c r="Q10" s="49">
         <f>P10*N10</f>
         <v>2.7159</v>
       </c>
       <c r="R10" s="48"/>
-      <c r="S10" s="49"/>
+      <c r="S10" s="81"/>
     </row>
     <row r="11" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -2806,111 +2805,111 @@
         <f t="shared" ref="B11:B84" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="G11" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>255</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J11" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="K11" s="50" t="s">
-        <v>301</v>
-      </c>
-      <c r="L11" s="51">
+      <c r="E11" s="84" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G11" s="83" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="I11" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J11" s="83" t="s">
+        <v>369</v>
+      </c>
+      <c r="K11" s="83" t="s">
+        <v>300</v>
+      </c>
+      <c r="L11" s="84">
         <v>3</v>
       </c>
-      <c r="M11" s="50">
+      <c r="M11" s="83">
         <f t="shared" ref="M11:M71" si="1">L11*5</f>
         <v>15</v>
       </c>
-      <c r="N11" s="50">
+      <c r="N11" s="83">
         <v>16</v>
       </c>
-      <c r="O11" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P11" s="54">
+      <c r="O11" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P11" s="86">
         <v>0.40799999999999997</v>
       </c>
-      <c r="Q11" s="54">
+      <c r="Q11" s="86">
         <f t="shared" ref="Q11:Q71" si="2">P11*N11</f>
         <v>6.5279999999999996</v>
       </c>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
-    </row>
-    <row r="12" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R11" s="87"/>
+      <c r="S11" s="87"/>
+    </row>
+    <row r="12" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="38">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="59" t="s">
-        <v>342</v>
+      <c r="C12" s="54" t="s">
+        <v>341</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>9</v>
+        <v>454</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L12" s="47">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M12" s="46">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N12" s="46">
         <v>100</v>
       </c>
-      <c r="O12" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P12" s="53">
+      <c r="O12" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P12" s="49">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="Q12" s="53">
+      <c r="Q12" s="49">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="R12" s="48"/>
-      <c r="S12" s="49"/>
+      <c r="S12" s="81"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -2918,55 +2917,55 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="G13" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="H13" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="I13" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J13" s="50" t="s">
-        <v>372</v>
-      </c>
-      <c r="K13" s="50" t="s">
-        <v>303</v>
-      </c>
-      <c r="L13" s="51">
-        <v>1</v>
-      </c>
-      <c r="M13" s="50">
+      <c r="C13" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="D13" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="83" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="83" t="s">
+        <v>256</v>
+      </c>
+      <c r="I13" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J13" s="83" t="s">
+        <v>371</v>
+      </c>
+      <c r="K13" s="83" t="s">
+        <v>302</v>
+      </c>
+      <c r="L13" s="84">
+        <v>1</v>
+      </c>
+      <c r="M13" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N13" s="50">
+      <c r="N13" s="83">
         <v>6</v>
       </c>
-      <c r="O13" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P13" s="54">
+      <c r="O13" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P13" s="86">
         <v>0.8125</v>
       </c>
-      <c r="Q13" s="54">
+      <c r="Q13" s="86">
         <f t="shared" si="2"/>
         <v>4.875</v>
       </c>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="87"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -2974,32 +2973,32 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="59" t="s">
-        <v>342</v>
+      <c r="C14" s="54" t="s">
+        <v>341</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L14" s="47">
         <v>4</v>
@@ -3011,18 +3010,18 @@
       <c r="N14" s="46">
         <v>30</v>
       </c>
-      <c r="O14" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P14" s="53">
+      <c r="O14" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P14" s="49">
         <v>3.5299999999999998E-2</v>
       </c>
-      <c r="Q14" s="53">
+      <c r="Q14" s="49">
         <f t="shared" si="2"/>
         <v>1.0589999999999999</v>
       </c>
       <c r="R14" s="48"/>
-      <c r="S14" s="49"/>
+      <c r="S14" s="81"/>
     </row>
     <row r="15" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
@@ -3030,55 +3029,55 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="G15" s="50" t="s">
-        <v>197</v>
-      </c>
-      <c r="H15" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J15" s="50" t="s">
-        <v>375</v>
-      </c>
-      <c r="K15" s="50" t="s">
-        <v>305</v>
-      </c>
-      <c r="L15" s="51">
+      <c r="C15" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="D15" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="84" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I15" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J15" s="83" t="s">
+        <v>374</v>
+      </c>
+      <c r="K15" s="83" t="s">
+        <v>304</v>
+      </c>
+      <c r="L15" s="84">
         <v>2</v>
       </c>
-      <c r="M15" s="50">
+      <c r="M15" s="83">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N15" s="50">
+      <c r="N15" s="83">
         <v>100</v>
       </c>
-      <c r="O15" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P15" s="54">
+      <c r="O15" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P15" s="86">
         <v>2.8E-3</v>
       </c>
-      <c r="Q15" s="54">
+      <c r="Q15" s="86">
         <f t="shared" si="2"/>
         <v>0.27999999999999997</v>
       </c>
-      <c r="R15" s="52"/>
-      <c r="S15" s="52"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
     </row>
     <row r="16" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -3086,32 +3085,32 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="59" t="s">
-        <v>342</v>
+      <c r="C16" s="54" t="s">
+        <v>341</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K16" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L16" s="47">
         <v>10</v>
@@ -3123,18 +3122,18 @@
       <c r="N16" s="46">
         <v>100</v>
       </c>
-      <c r="O16" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P16" s="53">
+      <c r="O16" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P16" s="49">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="Q16" s="53">
+      <c r="Q16" s="49">
         <f t="shared" si="2"/>
         <v>0.42</v>
       </c>
       <c r="R16" s="48"/>
-      <c r="S16" s="49"/>
+      <c r="S16" s="81"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
@@ -3142,55 +3141,55 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="H17" s="50" t="s">
-        <v>260</v>
-      </c>
-      <c r="I17" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J17" s="50" t="s">
-        <v>377</v>
-      </c>
-      <c r="K17" s="50" t="s">
-        <v>304</v>
-      </c>
-      <c r="L17" s="51">
+      <c r="C17" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="D17" s="83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="84" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17" s="83" t="s">
+        <v>259</v>
+      </c>
+      <c r="I17" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J17" s="83" t="s">
+        <v>376</v>
+      </c>
+      <c r="K17" s="83" t="s">
+        <v>303</v>
+      </c>
+      <c r="L17" s="84">
         <v>2</v>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="83">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N17" s="50">
+      <c r="N17" s="83">
         <v>20</v>
       </c>
-      <c r="O17" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P17" s="54">
+      <c r="O17" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P17" s="86">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="Q17" s="54">
+      <c r="Q17" s="86">
         <f t="shared" si="2"/>
         <v>0.28400000000000003</v>
       </c>
-      <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
+      <c r="R17" s="87"/>
+      <c r="S17" s="87"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -3198,32 +3197,32 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="59" t="s">
-        <v>342</v>
+      <c r="C18" s="54" t="s">
+        <v>341</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G18" s="47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L18" s="47">
         <v>1</v>
@@ -3235,18 +3234,18 @@
       <c r="N18" s="46">
         <v>100</v>
       </c>
-      <c r="O18" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P18" s="53">
+      <c r="O18" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P18" s="49">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="Q18" s="53">
+      <c r="Q18" s="49">
         <f t="shared" si="2"/>
         <v>0.51</v>
       </c>
       <c r="R18" s="48"/>
-      <c r="S18" s="49"/>
+      <c r="S18" s="81"/>
     </row>
     <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -3254,55 +3253,55 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D19" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="F19" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="G19" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J19" s="50" t="s">
-        <v>379</v>
-      </c>
-      <c r="K19" s="50" t="s">
-        <v>308</v>
-      </c>
-      <c r="L19" s="51">
+      <c r="C19" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="D19" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="H19" s="83" t="s">
+        <v>260</v>
+      </c>
+      <c r="I19" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J19" s="83" t="s">
+        <v>378</v>
+      </c>
+      <c r="K19" s="83" t="s">
+        <v>307</v>
+      </c>
+      <c r="L19" s="84">
         <v>2</v>
       </c>
-      <c r="M19" s="50">
+      <c r="M19" s="83">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N19" s="50">
+      <c r="N19" s="83">
         <v>20</v>
       </c>
-      <c r="O19" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P19" s="54">
+      <c r="O19" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P19" s="86">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="Q19" s="54">
+      <c r="Q19" s="86">
         <f t="shared" si="2"/>
         <v>0.65799999999999992</v>
       </c>
-      <c r="R19" s="52"/>
-      <c r="S19" s="52"/>
+      <c r="R19" s="87"/>
+      <c r="S19" s="87"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -3310,32 +3309,32 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="59" t="s">
-        <v>342</v>
+      <c r="C20" s="54" t="s">
+        <v>341</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L20" s="47">
         <v>2</v>
@@ -3347,18 +3346,18 @@
       <c r="N20" s="46">
         <v>100</v>
       </c>
-      <c r="O20" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P20" s="53">
+      <c r="O20" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P20" s="49">
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="Q20" s="53">
+      <c r="Q20" s="49">
         <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="R20" s="48"/>
-      <c r="S20" s="49"/>
+      <c r="S20" s="81"/>
     </row>
     <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -3366,55 +3365,55 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D21" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="H21" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J21" s="50" t="s">
-        <v>381</v>
-      </c>
-      <c r="K21" s="50" t="s">
-        <v>310</v>
-      </c>
-      <c r="L21" s="51">
-        <v>1</v>
-      </c>
-      <c r="M21" s="50">
+      <c r="C21" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="G21" s="83" t="s">
+        <v>202</v>
+      </c>
+      <c r="H21" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I21" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J21" s="83" t="s">
+        <v>380</v>
+      </c>
+      <c r="K21" s="83" t="s">
+        <v>309</v>
+      </c>
+      <c r="L21" s="84">
+        <v>1</v>
+      </c>
+      <c r="M21" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N21" s="50">
+      <c r="N21" s="83">
         <v>100</v>
       </c>
-      <c r="O21" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P21" s="54">
+      <c r="O21" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P21" s="86">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="Q21" s="54">
+      <c r="Q21" s="86">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="87"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -3422,32 +3421,32 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="59" t="s">
-        <v>342</v>
+      <c r="C22" s="54" t="s">
+        <v>341</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="G22" s="66" t="s">
-        <v>204</v>
+        <v>156</v>
+      </c>
+      <c r="G22" s="59" t="s">
+        <v>203</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I22" s="46" t="s">
+        <v>426</v>
+      </c>
+      <c r="J22" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="J22" s="46" t="s">
-        <v>428</v>
-      </c>
       <c r="K22" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L22" s="47">
         <v>2</v>
@@ -3459,18 +3458,18 @@
       <c r="N22" s="46">
         <v>20</v>
       </c>
-      <c r="O22" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P22" s="53">
+      <c r="O22" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P22" s="49">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="Q22" s="53">
+      <c r="Q22" s="49">
         <f t="shared" si="2"/>
         <v>0.6419999999999999</v>
       </c>
       <c r="R22" s="48"/>
-      <c r="S22" s="49"/>
+      <c r="S22" s="81"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -3478,55 +3477,55 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D23" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="G23" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="H23" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J23" s="50" t="s">
-        <v>382</v>
-      </c>
-      <c r="K23" s="50" t="s">
-        <v>312</v>
-      </c>
-      <c r="L23" s="51">
-        <v>1</v>
-      </c>
-      <c r="M23" s="50">
+      <c r="C23" s="82" t="s">
+        <v>341</v>
+      </c>
+      <c r="D23" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="84" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="G23" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="H23" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I23" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J23" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="K23" s="83" t="s">
+        <v>311</v>
+      </c>
+      <c r="L23" s="84">
+        <v>1</v>
+      </c>
+      <c r="M23" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N23" s="50">
+      <c r="N23" s="83">
         <v>100</v>
       </c>
-      <c r="O23" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P23" s="54">
+      <c r="O23" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P23" s="86">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="Q23" s="54">
+      <c r="Q23" s="86">
         <f t="shared" si="2"/>
         <v>0.38999999999999996</v>
       </c>
-      <c r="R23" s="52"/>
-      <c r="S23" s="52"/>
+      <c r="R23" s="87"/>
+      <c r="S23" s="87"/>
     </row>
     <row r="24" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -3534,32 +3533,32 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="59" t="s">
-        <v>343</v>
+      <c r="C24" s="54" t="s">
+        <v>342</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K24" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L24" s="47">
         <v>1</v>
@@ -3571,18 +3570,18 @@
       <c r="N24" s="46">
         <v>10</v>
       </c>
-      <c r="O24" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P24" s="53">
+      <c r="O24" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P24" s="49">
         <v>9.9699999999999997E-2</v>
       </c>
-      <c r="Q24" s="53">
+      <c r="Q24" s="49">
         <f t="shared" si="2"/>
         <v>0.997</v>
       </c>
       <c r="R24" s="48"/>
-      <c r="S24" s="49"/>
+      <c r="S24" s="81"/>
     </row>
     <row r="25" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -3590,55 +3589,55 @@
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="60" t="s">
-        <v>343</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="G25" s="50" t="s">
-        <v>208</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>264</v>
-      </c>
-      <c r="I25" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J25" s="50" t="s">
-        <v>383</v>
-      </c>
-      <c r="K25" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L25" s="51">
+      <c r="C25" s="82" t="s">
+        <v>342</v>
+      </c>
+      <c r="D25" s="83" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="83" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="83" t="s">
+        <v>207</v>
+      </c>
+      <c r="H25" s="83" t="s">
+        <v>263</v>
+      </c>
+      <c r="I25" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J25" s="83" t="s">
+        <v>382</v>
+      </c>
+      <c r="K25" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L25" s="84">
         <v>3</v>
       </c>
-      <c r="M25" s="50">
+      <c r="M25" s="83">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N25" s="50">
+      <c r="N25" s="83">
         <v>20</v>
       </c>
-      <c r="O25" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P25" s="54">
+      <c r="O25" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P25" s="86">
         <v>6.4199999999999993E-2</v>
       </c>
-      <c r="Q25" s="54">
+      <c r="Q25" s="86">
         <f t="shared" si="2"/>
         <v>1.2839999999999998</v>
       </c>
-      <c r="R25" s="52"/>
-      <c r="S25" s="52"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
     </row>
     <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -3646,32 +3645,32 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="59" t="s">
-        <v>343</v>
+      <c r="C26" s="54" t="s">
+        <v>342</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G26" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K26" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L26" s="47">
         <v>3</v>
@@ -3683,18 +3682,18 @@
       <c r="N26" s="46">
         <v>20</v>
       </c>
-      <c r="O26" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P26" s="53">
+      <c r="O26" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P26" s="49">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="Q26" s="53">
+      <c r="Q26" s="49">
         <f t="shared" si="2"/>
         <v>0.77799999999999991</v>
       </c>
       <c r="R26" s="48"/>
-      <c r="S26" s="49"/>
+      <c r="S26" s="81"/>
     </row>
     <row r="27" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -3702,55 +3701,55 @@
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="60" t="s">
-        <v>343</v>
-      </c>
-      <c r="D27" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="G27" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="H27" s="50" t="s">
-        <v>263</v>
-      </c>
-      <c r="I27" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J27" s="50" t="s">
-        <v>431</v>
-      </c>
-      <c r="K27" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L27" s="51">
+      <c r="C27" s="82" t="s">
+        <v>342</v>
+      </c>
+      <c r="D27" s="83" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="84" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="83" t="s">
+        <v>209</v>
+      </c>
+      <c r="H27" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="I27" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J27" s="83" t="s">
+        <v>430</v>
+      </c>
+      <c r="K27" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L27" s="84">
         <v>4</v>
       </c>
-      <c r="M27" s="50">
+      <c r="M27" s="83">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="50">
+      <c r="N27" s="83">
         <v>50</v>
       </c>
-      <c r="O27" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P27" s="54">
+      <c r="O27" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P27" s="86">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="Q27" s="54">
+      <c r="Q27" s="86">
         <f t="shared" si="2"/>
         <v>0.48499999999999999</v>
       </c>
-      <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
+      <c r="R27" s="87"/>
+      <c r="S27" s="87"/>
     </row>
     <row r="28" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -3758,32 +3757,32 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="59" t="s">
-        <v>343</v>
+      <c r="C28" s="54" t="s">
+        <v>342</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I28" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K28" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L28" s="47">
         <v>1</v>
@@ -3795,18 +3794,18 @@
       <c r="N28" s="46">
         <v>10</v>
       </c>
-      <c r="O28" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P28" s="53">
+      <c r="O28" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P28" s="49">
         <v>5.6399999999999999E-2</v>
       </c>
-      <c r="Q28" s="53">
+      <c r="Q28" s="49">
         <f t="shared" si="2"/>
         <v>0.56399999999999995</v>
       </c>
       <c r="R28" s="48"/>
-      <c r="S28" s="49"/>
+      <c r="S28" s="81"/>
     </row>
     <row r="29" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -3814,55 +3813,55 @@
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="60" t="s">
-        <v>343</v>
-      </c>
-      <c r="D29" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="F29" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="H29" s="50" t="s">
-        <v>267</v>
-      </c>
-      <c r="I29" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J29" s="50" t="s">
-        <v>433</v>
-      </c>
-      <c r="K29" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L29" s="51">
-        <v>1</v>
-      </c>
-      <c r="M29" s="50">
+      <c r="C29" s="82" t="s">
+        <v>342</v>
+      </c>
+      <c r="D29" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="84" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="83" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" s="83" t="s">
+        <v>210</v>
+      </c>
+      <c r="H29" s="83" t="s">
+        <v>266</v>
+      </c>
+      <c r="I29" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J29" s="83" t="s">
+        <v>432</v>
+      </c>
+      <c r="K29" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L29" s="84">
+        <v>1</v>
+      </c>
+      <c r="M29" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N29" s="50">
+      <c r="N29" s="83">
         <v>10</v>
       </c>
-      <c r="O29" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P29" s="54">
+      <c r="O29" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P29" s="86">
         <v>6.5100000000000005E-2</v>
       </c>
-      <c r="Q29" s="54">
+      <c r="Q29" s="86">
         <f t="shared" si="2"/>
         <v>0.65100000000000002</v>
       </c>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
+      <c r="R29" s="87"/>
+      <c r="S29" s="87"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -3870,32 +3869,32 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="59" t="s">
-        <v>343</v>
+      <c r="C30" s="54" t="s">
+        <v>342</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I30" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K30" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L30" s="47">
         <v>1</v>
@@ -3907,18 +3906,18 @@
       <c r="N30" s="46">
         <v>20</v>
       </c>
-      <c r="O30" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P30" s="53">
+      <c r="O30" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P30" s="49">
         <v>2.5499999999999998E-2</v>
       </c>
-      <c r="Q30" s="53">
+      <c r="Q30" s="49">
         <f t="shared" si="2"/>
         <v>0.51</v>
       </c>
       <c r="R30" s="48"/>
-      <c r="S30" s="49"/>
+      <c r="S30" s="81"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3926,55 +3925,55 @@
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="60" t="s">
-        <v>344</v>
-      </c>
-      <c r="D31" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="G31" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="I31" s="50" t="s">
+      <c r="C31" s="82" t="s">
+        <v>343</v>
+      </c>
+      <c r="D31" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G31" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="H31" s="83" t="s">
+        <v>268</v>
+      </c>
+      <c r="I31" s="83" t="s">
+        <v>433</v>
+      </c>
+      <c r="J31" s="83" t="s">
         <v>434</v>
       </c>
-      <c r="J31" s="50" t="s">
-        <v>435</v>
-      </c>
-      <c r="K31" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L31" s="51">
-        <v>1</v>
-      </c>
-      <c r="M31" s="50">
+      <c r="K31" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L31" s="84">
+        <v>1</v>
+      </c>
+      <c r="M31" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N31" s="50">
+      <c r="N31" s="83">
         <v>10</v>
       </c>
-      <c r="O31" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P31" s="54">
+      <c r="O31" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P31" s="86">
         <v>0.1207</v>
       </c>
-      <c r="Q31" s="54">
+      <c r="Q31" s="86">
         <f t="shared" si="2"/>
         <v>1.2070000000000001</v>
       </c>
-      <c r="R31" s="52"/>
-      <c r="S31" s="52"/>
+      <c r="R31" s="87"/>
+      <c r="S31" s="87"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -3982,32 +3981,32 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="59" t="s">
-        <v>344</v>
+      <c r="C32" s="54" t="s">
+        <v>343</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>355</v>
-      </c>
-      <c r="G32" s="66" t="s">
-        <v>165</v>
+        <v>354</v>
+      </c>
+      <c r="G32" s="59" t="s">
+        <v>164</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I32" s="46" t="s">
+        <v>435</v>
+      </c>
+      <c r="J32" s="46" t="s">
         <v>436</v>
       </c>
-      <c r="J32" s="46" t="s">
-        <v>437</v>
-      </c>
       <c r="K32" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L32" s="47">
         <v>1</v>
@@ -4019,18 +4018,18 @@
       <c r="N32" s="46">
         <v>10</v>
       </c>
-      <c r="O32" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P32" s="53">
+      <c r="O32" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P32" s="49">
         <v>7.0300000000000001E-2</v>
       </c>
-      <c r="Q32" s="53">
+      <c r="Q32" s="49">
         <f t="shared" si="2"/>
         <v>0.70300000000000007</v>
       </c>
       <c r="R32" s="48"/>
-      <c r="S32" s="49"/>
+      <c r="S32" s="81"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -4038,55 +4037,55 @@
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="D33" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="F33" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="G33" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="H33" s="50" t="s">
-        <v>270</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J33" s="50" t="s">
-        <v>385</v>
-      </c>
-      <c r="K33" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L33" s="51">
-        <v>1</v>
-      </c>
-      <c r="M33" s="50">
+      <c r="C33" s="82" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="84" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" s="83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G33" s="83" t="s">
+        <v>212</v>
+      </c>
+      <c r="H33" s="83" t="s">
+        <v>269</v>
+      </c>
+      <c r="I33" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J33" s="83" t="s">
+        <v>384</v>
+      </c>
+      <c r="K33" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L33" s="84">
+        <v>1</v>
+      </c>
+      <c r="M33" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N33" s="50">
+      <c r="N33" s="83">
         <v>10</v>
       </c>
-      <c r="O33" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P33" s="54">
+      <c r="O33" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P33" s="86">
         <v>8.8400000000000006E-2</v>
       </c>
-      <c r="Q33" s="54">
+      <c r="Q33" s="86">
         <f t="shared" si="2"/>
         <v>0.88400000000000012</v>
       </c>
-      <c r="R33" s="52"/>
-      <c r="S33" s="52"/>
+      <c r="R33" s="87"/>
+      <c r="S33" s="87"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -4094,32 +4093,32 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>346</v>
+      <c r="C34" s="54" t="s">
+        <v>345</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G34" s="47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I34" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K34" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L34" s="47">
         <v>1</v>
@@ -4131,18 +4130,18 @@
       <c r="N34" s="46">
         <v>10</v>
       </c>
-      <c r="O34" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P34" s="53">
+      <c r="O34" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P34" s="49">
         <v>6.0900000000000003E-2</v>
       </c>
-      <c r="Q34" s="53">
+      <c r="Q34" s="49">
         <f t="shared" si="2"/>
         <v>0.60899999999999999</v>
       </c>
       <c r="R34" s="48"/>
-      <c r="S34" s="49"/>
+      <c r="S34" s="81"/>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -4150,55 +4149,55 @@
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="D35" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="F35" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="G35" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="H35" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="I35" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J35" s="50" t="s">
-        <v>387</v>
-      </c>
-      <c r="K35" s="50" t="s">
-        <v>313</v>
-      </c>
-      <c r="L35" s="51">
-        <v>1</v>
-      </c>
-      <c r="M35" s="50">
+      <c r="C35" s="82" t="s">
+        <v>346</v>
+      </c>
+      <c r="D35" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G35" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="H35" s="83" t="s">
+        <v>264</v>
+      </c>
+      <c r="I35" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J35" s="83" t="s">
+        <v>386</v>
+      </c>
+      <c r="K35" s="83" t="s">
+        <v>312</v>
+      </c>
+      <c r="L35" s="84">
+        <v>1</v>
+      </c>
+      <c r="M35" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N35" s="50">
+      <c r="N35" s="83">
         <v>6</v>
       </c>
-      <c r="O35" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P35" s="54">
+      <c r="O35" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P35" s="86">
         <v>0.754</v>
       </c>
-      <c r="Q35" s="54">
+      <c r="Q35" s="86">
         <f t="shared" si="2"/>
         <v>4.524</v>
       </c>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
+      <c r="R35" s="87"/>
+      <c r="S35" s="87"/>
     </row>
     <row r="36" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -4206,32 +4205,32 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="59" t="s">
-        <v>347</v>
+      <c r="C36" s="54" t="s">
+        <v>346</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F36" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K36" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L36" s="47">
         <v>1</v>
@@ -4243,18 +4242,18 @@
       <c r="N36" s="46">
         <v>10</v>
       </c>
-      <c r="O36" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P36" s="53">
+      <c r="O36" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P36" s="49">
         <v>8.3299999999999999E-2</v>
       </c>
-      <c r="Q36" s="53">
+      <c r="Q36" s="49">
         <f t="shared" si="2"/>
         <v>0.83299999999999996</v>
       </c>
       <c r="R36" s="48"/>
-      <c r="S36" s="49"/>
+      <c r="S36" s="81"/>
     </row>
     <row r="37" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
@@ -4262,55 +4261,55 @@
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="D37" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="F37" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="G37" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="H37" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="I37" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J37" s="50" t="s">
-        <v>389</v>
-      </c>
-      <c r="K37" s="50" t="s">
-        <v>315</v>
-      </c>
-      <c r="L37" s="51">
-        <v>1</v>
-      </c>
-      <c r="M37" s="50">
+      <c r="C37" s="82" t="s">
+        <v>346</v>
+      </c>
+      <c r="D37" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="84" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="83" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" s="83" t="s">
+        <v>214</v>
+      </c>
+      <c r="H37" s="83" t="s">
+        <v>271</v>
+      </c>
+      <c r="I37" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J37" s="83" t="s">
+        <v>388</v>
+      </c>
+      <c r="K37" s="83" t="s">
+        <v>314</v>
+      </c>
+      <c r="L37" s="84">
+        <v>1</v>
+      </c>
+      <c r="M37" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N37" s="50">
+      <c r="N37" s="83">
         <v>10</v>
       </c>
-      <c r="O37" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P37" s="54">
+      <c r="O37" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P37" s="86">
         <v>2.7300000000000001E-2</v>
       </c>
-      <c r="Q37" s="54">
+      <c r="Q37" s="86">
         <f t="shared" si="2"/>
         <v>0.27300000000000002</v>
       </c>
-      <c r="R37" s="52"/>
-      <c r="S37" s="52"/>
+      <c r="R37" s="87"/>
+      <c r="S37" s="87"/>
     </row>
     <row r="38" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -4318,32 +4317,32 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="59" t="s">
-        <v>348</v>
+      <c r="C38" s="54" t="s">
+        <v>347</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="G38" s="66" t="s">
-        <v>216</v>
+        <v>169</v>
+      </c>
+      <c r="G38" s="59" t="s">
+        <v>215</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I38" s="46" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J38" s="46" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K38" s="46" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L38" s="47">
         <v>8</v>
@@ -4355,18 +4354,18 @@
       <c r="N38" s="46">
         <v>50</v>
       </c>
-      <c r="O38" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P38" s="53">
+      <c r="O38" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P38" s="49">
         <v>1.5900000000000001E-2</v>
       </c>
-      <c r="Q38" s="53">
+      <c r="Q38" s="49">
         <f t="shared" si="2"/>
         <v>0.79500000000000004</v>
       </c>
       <c r="R38" s="48"/>
-      <c r="S38" s="49"/>
+      <c r="S38" s="81"/>
     </row>
     <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
@@ -4374,55 +4373,55 @@
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="D39" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="F39" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="G39" s="67" t="s">
-        <v>217</v>
-      </c>
-      <c r="H39" s="50" t="s">
-        <v>273</v>
-      </c>
-      <c r="I39" s="50" t="s">
+      <c r="C39" s="82" t="s">
+        <v>347</v>
+      </c>
+      <c r="D39" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="G39" s="88" t="s">
+        <v>216</v>
+      </c>
+      <c r="H39" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="I39" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="J39" s="83" t="s">
         <v>438</v>
       </c>
-      <c r="J39" s="50" t="s">
-        <v>439</v>
-      </c>
-      <c r="K39" s="50" t="s">
-        <v>317</v>
-      </c>
-      <c r="L39" s="51">
-        <v>1</v>
-      </c>
-      <c r="M39" s="50">
+      <c r="K39" s="83" t="s">
+        <v>316</v>
+      </c>
+      <c r="L39" s="84">
+        <v>1</v>
+      </c>
+      <c r="M39" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N39" s="50">
+      <c r="N39" s="83">
         <v>10</v>
       </c>
-      <c r="O39" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P39" s="54">
+      <c r="O39" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P39" s="86">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="Q39" s="54">
+      <c r="Q39" s="86">
         <f t="shared" si="2"/>
         <v>0.39200000000000002</v>
       </c>
-      <c r="R39" s="52"/>
-      <c r="S39" s="52"/>
+      <c r="R39" s="87"/>
+      <c r="S39" s="87"/>
     </row>
     <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
@@ -4430,32 +4429,32 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="59" t="s">
-        <v>349</v>
+      <c r="C40" s="54" t="s">
+        <v>348</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G40" s="47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I40" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K40" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L40" s="47">
         <v>1</v>
@@ -4467,18 +4466,18 @@
       <c r="N40" s="46">
         <v>6</v>
       </c>
-      <c r="O40" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P40" s="53">
+      <c r="O40" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P40" s="49">
         <v>0.48880000000000001</v>
       </c>
-      <c r="Q40" s="53">
+      <c r="Q40" s="49">
         <f t="shared" si="2"/>
         <v>2.9328000000000003</v>
       </c>
       <c r="R40" s="48"/>
-      <c r="S40" s="49"/>
+      <c r="S40" s="81"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -4486,55 +4485,55 @@
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="60" t="s">
-        <v>350</v>
-      </c>
-      <c r="D41" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="F41" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="G41" s="67" t="s">
-        <v>218</v>
-      </c>
-      <c r="H41" s="50" t="s">
-        <v>275</v>
-      </c>
-      <c r="I41" s="50" t="s">
+      <c r="C41" s="82" t="s">
+        <v>349</v>
+      </c>
+      <c r="D41" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="84" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="G41" s="88" t="s">
+        <v>217</v>
+      </c>
+      <c r="H41" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="I41" s="83" t="s">
+        <v>441</v>
+      </c>
+      <c r="J41" s="83" t="s">
         <v>442</v>
       </c>
-      <c r="J41" s="50" t="s">
-        <v>443</v>
-      </c>
-      <c r="K41" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L41" s="51">
-        <v>1</v>
-      </c>
-      <c r="M41" s="50">
+      <c r="K41" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L41" s="84">
+        <v>1</v>
+      </c>
+      <c r="M41" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N41" s="50">
+      <c r="N41" s="83">
         <v>20</v>
       </c>
-      <c r="O41" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P41" s="54">
+      <c r="O41" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P41" s="86">
         <v>3.2599999999999997E-2</v>
       </c>
-      <c r="Q41" s="54">
+      <c r="Q41" s="86">
         <f t="shared" si="2"/>
         <v>0.65199999999999991</v>
       </c>
-      <c r="R41" s="52"/>
-      <c r="S41" s="52"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="87"/>
     </row>
     <row r="42" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -4542,32 +4541,32 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="59" t="s">
-        <v>346</v>
+      <c r="C42" s="54" t="s">
+        <v>345</v>
       </c>
       <c r="D42" s="46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F42" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G42" s="47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I42" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J42" s="46" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L42" s="47">
         <v>1</v>
@@ -4579,18 +4578,18 @@
       <c r="N42" s="46">
         <v>10</v>
       </c>
-      <c r="O42" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P42" s="53">
+      <c r="O42" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P42" s="49">
         <v>5.8099999999999999E-2</v>
       </c>
-      <c r="Q42" s="53">
+      <c r="Q42" s="49">
         <f t="shared" si="2"/>
         <v>0.58099999999999996</v>
       </c>
       <c r="R42" s="48"/>
-      <c r="S42" s="49"/>
+      <c r="S42" s="81"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -4598,55 +4597,55 @@
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="60" t="s">
-        <v>350</v>
-      </c>
-      <c r="D43" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="F43" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="G43" s="67">
+      <c r="C43" s="82" t="s">
+        <v>349</v>
+      </c>
+      <c r="D43" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="84" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43" s="83" t="s">
+        <v>173</v>
+      </c>
+      <c r="G43" s="88">
         <v>61300611121</v>
       </c>
-      <c r="H43" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="I43" s="50" t="s">
+      <c r="H43" s="83" t="s">
+        <v>276</v>
+      </c>
+      <c r="I43" s="83" t="s">
+        <v>443</v>
+      </c>
+      <c r="J43" s="83" t="s">
         <v>444</v>
       </c>
-      <c r="J43" s="50" t="s">
-        <v>445</v>
-      </c>
-      <c r="K43" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L43" s="51">
-        <v>1</v>
-      </c>
-      <c r="M43" s="50">
+      <c r="K43" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L43" s="84">
+        <v>1</v>
+      </c>
+      <c r="M43" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N43" s="50">
+      <c r="N43" s="83">
         <v>20</v>
       </c>
-      <c r="O43" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P43" s="54">
+      <c r="O43" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P43" s="86">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="Q43" s="54">
+      <c r="Q43" s="86">
         <f t="shared" si="2"/>
         <v>0.71</v>
       </c>
-      <c r="R43" s="52"/>
-      <c r="S43" s="52"/>
+      <c r="R43" s="87"/>
+      <c r="S43" s="87"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -4654,26 +4653,26 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="59" t="s">
-        <v>318</v>
+      <c r="C44" s="54" t="s">
+        <v>317</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G44" s="47" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H44" s="46"/>
       <c r="I44" s="46"/>
       <c r="J44" s="46"/>
       <c r="K44" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L44" s="47">
         <v>2</v>
@@ -4683,14 +4682,14 @@
         <v>10</v>
       </c>
       <c r="N44" s="46"/>
-      <c r="O44" s="64"/>
-      <c r="P44" s="53"/>
-      <c r="Q44" s="53">
+      <c r="O44" s="58"/>
+      <c r="P44" s="49"/>
+      <c r="Q44" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R44" s="48"/>
-      <c r="S44" s="49"/>
+      <c r="S44" s="81"/>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
@@ -4698,55 +4697,55 @@
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="60" t="s">
-        <v>351</v>
-      </c>
-      <c r="D45" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="E45" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="F45" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G45" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="H45" s="50" t="s">
-        <v>278</v>
-      </c>
-      <c r="I45" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J45" s="50" t="s">
-        <v>392</v>
-      </c>
-      <c r="K45" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L45" s="51">
+      <c r="C45" s="82" t="s">
+        <v>350</v>
+      </c>
+      <c r="D45" s="83" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="G45" s="83" t="s">
+        <v>218</v>
+      </c>
+      <c r="H45" s="83" t="s">
+        <v>277</v>
+      </c>
+      <c r="I45" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J45" s="83" t="s">
+        <v>391</v>
+      </c>
+      <c r="K45" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L45" s="84">
         <v>6</v>
       </c>
-      <c r="M45" s="50">
+      <c r="M45" s="83">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N45" s="50">
+      <c r="N45" s="83">
         <v>40</v>
       </c>
-      <c r="O45" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P45" s="54">
+      <c r="O45" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P45" s="86">
         <v>2.9600000000000001E-2</v>
       </c>
-      <c r="Q45" s="54">
+      <c r="Q45" s="86">
         <f t="shared" si="2"/>
         <v>1.1840000000000002</v>
       </c>
-      <c r="R45" s="52"/>
-      <c r="S45" s="52"/>
+      <c r="R45" s="87"/>
+      <c r="S45" s="87"/>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
@@ -4754,32 +4753,32 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="59" t="s">
-        <v>351</v>
+      <c r="C46" s="54" t="s">
+        <v>350</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F46" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G46" s="47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H46" s="46" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I46" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J46" s="46" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K46" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L46" s="47">
         <v>4</v>
@@ -4791,18 +4790,18 @@
       <c r="N46" s="46">
         <v>22</v>
       </c>
-      <c r="O46" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P46" s="53">
+      <c r="O46" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P46" s="49">
         <v>1.4046000000000001</v>
       </c>
-      <c r="Q46" s="53">
+      <c r="Q46" s="49">
         <f t="shared" si="2"/>
         <v>30.901200000000003</v>
       </c>
       <c r="R46" s="48"/>
-      <c r="S46" s="49"/>
+      <c r="S46" s="81"/>
     </row>
     <row r="47" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
@@ -4810,55 +4809,55 @@
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="60" t="s">
-        <v>351</v>
-      </c>
-      <c r="D47" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="E47" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="50" t="s">
-        <v>357</v>
-      </c>
-      <c r="G47" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="H47" s="50" t="s">
-        <v>280</v>
-      </c>
-      <c r="I47" s="50" t="s">
+      <c r="C47" s="82" t="s">
+        <v>350</v>
+      </c>
+      <c r="D47" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" s="84" t="s">
+        <v>115</v>
+      </c>
+      <c r="F47" s="83" t="s">
         <v>356</v>
       </c>
-      <c r="J47" s="50" t="s">
-        <v>394</v>
-      </c>
-      <c r="K47" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L47" s="51">
-        <v>1</v>
-      </c>
-      <c r="M47" s="50">
+      <c r="G47" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="H47" s="83" t="s">
+        <v>279</v>
+      </c>
+      <c r="I47" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J47" s="83" t="s">
+        <v>393</v>
+      </c>
+      <c r="K47" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L47" s="84">
+        <v>1</v>
+      </c>
+      <c r="M47" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N47" s="50">
+      <c r="N47" s="83">
         <v>6</v>
       </c>
-      <c r="O47" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P47" s="54">
+      <c r="O47" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P47" s="86">
         <v>0.4355</v>
       </c>
-      <c r="Q47" s="54">
+      <c r="Q47" s="86">
         <f t="shared" si="2"/>
         <v>2.613</v>
       </c>
-      <c r="R47" s="52"/>
-      <c r="S47" s="52"/>
+      <c r="R47" s="87"/>
+      <c r="S47" s="87"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
@@ -4866,32 +4865,32 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="59" t="s">
-        <v>285</v>
+      <c r="C48" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G48" s="47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I48" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J48" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K48" s="46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L48" s="47">
         <v>1</v>
@@ -4903,18 +4902,18 @@
       <c r="N48" s="46">
         <v>100</v>
       </c>
-      <c r="O48" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P48" s="53">
+      <c r="O48" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P48" s="49">
         <v>1.4E-3</v>
       </c>
-      <c r="Q48" s="53">
+      <c r="Q48" s="49">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="R48" s="48"/>
-      <c r="S48" s="49"/>
+      <c r="S48" s="81"/>
     </row>
     <row r="49" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
@@ -4922,55 +4921,55 @@
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D49" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="E49" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="F49" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="G49" s="50" t="s">
-        <v>222</v>
-      </c>
-      <c r="H49" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="I49" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J49" s="50" t="s">
-        <v>396</v>
-      </c>
-      <c r="K49" s="50" t="s">
-        <v>320</v>
-      </c>
-      <c r="L49" s="51">
-        <v>1</v>
-      </c>
-      <c r="M49" s="50">
+      <c r="C49" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" s="83" t="s">
+        <v>44</v>
+      </c>
+      <c r="E49" s="84" t="s">
+        <v>117</v>
+      </c>
+      <c r="F49" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G49" s="83" t="s">
+        <v>221</v>
+      </c>
+      <c r="H49" s="83" t="s">
+        <v>280</v>
+      </c>
+      <c r="I49" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J49" s="83" t="s">
+        <v>395</v>
+      </c>
+      <c r="K49" s="83" t="s">
+        <v>319</v>
+      </c>
+      <c r="L49" s="84">
+        <v>1</v>
+      </c>
+      <c r="M49" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N49" s="50">
+      <c r="N49" s="83">
         <v>20</v>
       </c>
-      <c r="O49" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P49" s="54">
+      <c r="O49" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P49" s="86">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="Q49" s="54">
+      <c r="Q49" s="86">
         <f t="shared" si="2"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R49" s="52"/>
-      <c r="S49" s="52"/>
+      <c r="R49" s="87"/>
+      <c r="S49" s="87"/>
     </row>
     <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
@@ -4978,32 +4977,32 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="59" t="s">
-        <v>285</v>
+      <c r="C50" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D50" s="46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G50" s="47" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H50" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I50" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K50" s="46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L50" s="47">
         <v>2</v>
@@ -5015,18 +5014,18 @@
       <c r="N50" s="46">
         <v>20</v>
       </c>
-      <c r="O50" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P50" s="53">
+      <c r="O50" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P50" s="49">
         <v>3.0599999999999999E-2</v>
       </c>
-      <c r="Q50" s="53">
+      <c r="Q50" s="49">
         <f t="shared" si="2"/>
         <v>0.61199999999999999</v>
       </c>
       <c r="R50" s="48"/>
-      <c r="S50" s="49"/>
+      <c r="S50" s="81"/>
     </row>
     <row r="51" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -5034,55 +5033,55 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D51" s="50" t="s">
-        <v>447</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="F51" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="G51" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="H51" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I51" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J51" s="50" t="s">
-        <v>398</v>
-      </c>
-      <c r="K51" s="50" t="s">
-        <v>322</v>
-      </c>
-      <c r="L51" s="51">
-        <v>1</v>
-      </c>
-      <c r="M51" s="50">
+      <c r="C51" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D51" s="83" t="s">
+        <v>446</v>
+      </c>
+      <c r="E51" s="84" t="s">
+        <v>119</v>
+      </c>
+      <c r="F51" s="83" t="s">
+        <v>179</v>
+      </c>
+      <c r="G51" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="H51" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I51" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J51" s="83" t="s">
+        <v>397</v>
+      </c>
+      <c r="K51" s="83" t="s">
+        <v>321</v>
+      </c>
+      <c r="L51" s="84">
+        <v>1</v>
+      </c>
+      <c r="M51" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N51" s="50">
+      <c r="N51" s="83">
         <v>100</v>
       </c>
-      <c r="O51" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P51" s="54">
+      <c r="O51" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P51" s="86">
         <v>1E-3</v>
       </c>
-      <c r="Q51" s="54">
+      <c r="Q51" s="86">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R51" s="52"/>
-      <c r="S51" s="52"/>
+      <c r="R51" s="87"/>
+      <c r="S51" s="87"/>
     </row>
     <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -5090,32 +5089,32 @@
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="59" t="s">
-        <v>285</v>
+      <c r="C52" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D52" s="46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G52" s="47" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I52" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J52" s="46" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K52" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L52" s="47">
         <v>7</v>
@@ -5127,18 +5126,18 @@
       <c r="N52" s="46">
         <v>100</v>
       </c>
-      <c r="O52" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P52" s="53">
+      <c r="O52" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P52" s="49">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="Q52" s="53">
+      <c r="Q52" s="49">
         <f t="shared" si="2"/>
         <v>0.16999999999999998</v>
       </c>
       <c r="R52" s="48"/>
-      <c r="S52" s="49"/>
+      <c r="S52" s="81"/>
     </row>
     <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -5146,45 +5145,45 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D53" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="E53" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="F53" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="G53" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H53" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="I53" s="50"/>
-      <c r="J53" s="50"/>
-      <c r="K53" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="L53" s="51">
-        <v>1</v>
-      </c>
-      <c r="M53" s="50">
+      <c r="C53" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="E53" s="84" t="s">
+        <v>121</v>
+      </c>
+      <c r="F53" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G53" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="H53" s="83" t="s">
+        <v>281</v>
+      </c>
+      <c r="I53" s="83"/>
+      <c r="J53" s="83"/>
+      <c r="K53" s="83" t="s">
+        <v>323</v>
+      </c>
+      <c r="L53" s="84">
+        <v>1</v>
+      </c>
+      <c r="M53" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N53" s="50"/>
-      <c r="O53" s="65"/>
-      <c r="P53" s="54"/>
-      <c r="Q53" s="54">
+      <c r="N53" s="83"/>
+      <c r="O53" s="85"/>
+      <c r="P53" s="86"/>
+      <c r="Q53" s="86">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R53" s="52"/>
-      <c r="S53" s="52"/>
+      <c r="R53" s="87"/>
+      <c r="S53" s="87"/>
     </row>
     <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -5192,32 +5191,32 @@
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="59" t="s">
-        <v>285</v>
+      <c r="C54" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D54" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F54" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G54" s="47" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H54" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I54" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J54" s="46" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K54" s="46" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L54" s="47">
         <v>1</v>
@@ -5229,18 +5228,18 @@
       <c r="N54" s="46">
         <v>100</v>
       </c>
-      <c r="O54" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P54" s="53">
+      <c r="O54" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P54" s="49">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q54" s="53">
+      <c r="Q54" s="49">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
       <c r="R54" s="48"/>
-      <c r="S54" s="49"/>
+      <c r="S54" s="81"/>
     </row>
     <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
@@ -5248,55 +5247,55 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D55" s="50" t="s">
-        <v>448</v>
-      </c>
-      <c r="E55" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="F55" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="G55" s="50" t="s">
-        <v>229</v>
-      </c>
-      <c r="H55" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I55" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J55" s="50" t="s">
-        <v>401</v>
-      </c>
-      <c r="K55" s="50" t="s">
-        <v>326</v>
-      </c>
-      <c r="L55" s="51">
-        <v>1</v>
-      </c>
-      <c r="M55" s="50">
+      <c r="C55" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D55" s="83" t="s">
+        <v>447</v>
+      </c>
+      <c r="E55" s="84" t="s">
+        <v>123</v>
+      </c>
+      <c r="F55" s="83" t="s">
+        <v>179</v>
+      </c>
+      <c r="G55" s="83" t="s">
+        <v>228</v>
+      </c>
+      <c r="H55" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I55" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J55" s="83" t="s">
+        <v>400</v>
+      </c>
+      <c r="K55" s="83" t="s">
+        <v>325</v>
+      </c>
+      <c r="L55" s="84">
+        <v>1</v>
+      </c>
+      <c r="M55" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N55" s="50">
+      <c r="N55" s="83">
         <v>100</v>
       </c>
-      <c r="O55" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P55" s="54">
+      <c r="O55" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P55" s="86">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q55" s="54">
+      <c r="Q55" s="86">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="R55" s="52"/>
-      <c r="S55" s="52"/>
+      <c r="R55" s="87"/>
+      <c r="S55" s="87"/>
     </row>
     <row r="56" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
@@ -5304,32 +5303,32 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="59" t="s">
-        <v>285</v>
+      <c r="C56" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D56" s="46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G56" s="47" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I56" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J56" s="46" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K56" s="46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L56" s="47">
         <v>1</v>
@@ -5341,18 +5340,18 @@
       <c r="N56" s="46">
         <v>20</v>
       </c>
-      <c r="O56" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P56" s="53">
+      <c r="O56" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P56" s="49">
         <v>3.0300000000000001E-2</v>
       </c>
-      <c r="Q56" s="53">
+      <c r="Q56" s="49">
         <f t="shared" si="2"/>
         <v>0.60599999999999998</v>
       </c>
       <c r="R56" s="48"/>
-      <c r="S56" s="49"/>
+      <c r="S56" s="81"/>
     </row>
     <row r="57" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
@@ -5360,55 +5359,55 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D57" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="F57" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="G57" s="50" t="s">
-        <v>231</v>
-      </c>
-      <c r="H57" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I57" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J57" s="50" t="s">
-        <v>403</v>
-      </c>
-      <c r="K57" s="50" t="s">
-        <v>328</v>
-      </c>
-      <c r="L57" s="51">
+      <c r="C57" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D57" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="84" t="s">
+        <v>125</v>
+      </c>
+      <c r="F57" s="83" t="s">
+        <v>179</v>
+      </c>
+      <c r="G57" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="H57" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I57" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J57" s="83" t="s">
+        <v>402</v>
+      </c>
+      <c r="K57" s="83" t="s">
+        <v>327</v>
+      </c>
+      <c r="L57" s="84">
         <v>8</v>
       </c>
-      <c r="M57" s="50">
+      <c r="M57" s="83">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N57" s="50">
+      <c r="N57" s="83">
         <v>100</v>
       </c>
-      <c r="O57" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P57" s="54">
+      <c r="O57" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P57" s="86">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q57" s="54">
+      <c r="Q57" s="86">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="R57" s="52"/>
-      <c r="S57" s="52"/>
+      <c r="R57" s="87"/>
+      <c r="S57" s="87"/>
     </row>
     <row r="58" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
@@ -5416,32 +5415,32 @@
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
-      <c r="C58" s="59" t="s">
-        <v>285</v>
+      <c r="C58" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E58" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G58" s="47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I58" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J58" s="46" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K58" s="46" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L58" s="47">
         <v>1</v>
@@ -5453,18 +5452,18 @@
       <c r="N58" s="46">
         <v>10</v>
       </c>
-      <c r="O58" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P58" s="53">
+      <c r="O58" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P58" s="49">
         <v>8.3900000000000002E-2</v>
       </c>
-      <c r="Q58" s="53">
+      <c r="Q58" s="49">
         <f t="shared" si="2"/>
         <v>0.83899999999999997</v>
       </c>
       <c r="R58" s="48"/>
-      <c r="S58" s="49"/>
+      <c r="S58" s="81"/>
     </row>
     <row r="59" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
@@ -5472,55 +5471,55 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D59" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="E59" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="F59" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="G59" s="50" t="s">
-        <v>232</v>
-      </c>
-      <c r="H59" s="50" t="s">
+      <c r="C59" s="82" t="s">
         <v>284</v>
       </c>
-      <c r="I59" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J59" s="50" t="s">
-        <v>405</v>
-      </c>
-      <c r="K59" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="L59" s="51">
+      <c r="D59" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" s="84" t="s">
+        <v>127</v>
+      </c>
+      <c r="F59" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G59" s="83" t="s">
+        <v>231</v>
+      </c>
+      <c r="H59" s="83" t="s">
+        <v>283</v>
+      </c>
+      <c r="I59" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J59" s="83" t="s">
+        <v>404</v>
+      </c>
+      <c r="K59" s="83" t="s">
+        <v>328</v>
+      </c>
+      <c r="L59" s="84">
         <v>3</v>
       </c>
-      <c r="M59" s="50">
+      <c r="M59" s="83">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N59" s="50">
+      <c r="N59" s="83">
         <v>100</v>
       </c>
-      <c r="O59" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P59" s="54">
+      <c r="O59" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P59" s="86">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q59" s="54">
+      <c r="Q59" s="86">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="R59" s="52"/>
-      <c r="S59" s="52"/>
+      <c r="R59" s="87"/>
+      <c r="S59" s="87"/>
     </row>
     <row r="60" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
@@ -5528,32 +5527,32 @@
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="59" t="s">
-        <v>285</v>
+      <c r="C60" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G60" s="47" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H60" s="46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J60" s="46" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K60" s="46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L60" s="47">
         <v>1</v>
@@ -5565,18 +5564,18 @@
       <c r="N60" s="46">
         <v>10</v>
       </c>
-      <c r="O60" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P60" s="53">
+      <c r="O60" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P60" s="49">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="Q60" s="53">
+      <c r="Q60" s="49">
         <f t="shared" si="2"/>
         <v>0.64</v>
       </c>
       <c r="R60" s="48"/>
-      <c r="S60" s="49"/>
+      <c r="S60" s="81"/>
     </row>
     <row r="61" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
@@ -5584,55 +5583,55 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D61" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="E61" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="F61" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="G61" s="50" t="s">
-        <v>234</v>
-      </c>
-      <c r="H61" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I61" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J61" s="50" t="s">
-        <v>407</v>
-      </c>
-      <c r="K61" s="50" t="s">
-        <v>331</v>
-      </c>
-      <c r="L61" s="51">
+      <c r="C61" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D61" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" s="84" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G61" s="83" t="s">
+        <v>233</v>
+      </c>
+      <c r="H61" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I61" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J61" s="83" t="s">
+        <v>406</v>
+      </c>
+      <c r="K61" s="83" t="s">
+        <v>330</v>
+      </c>
+      <c r="L61" s="84">
         <v>4</v>
       </c>
-      <c r="M61" s="50">
+      <c r="M61" s="83">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="50">
+      <c r="N61" s="83">
         <v>100</v>
       </c>
-      <c r="O61" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P61" s="54">
+      <c r="O61" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P61" s="86">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q61" s="54">
+      <c r="Q61" s="86">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="R61" s="52"/>
-      <c r="S61" s="52"/>
+      <c r="R61" s="87"/>
+      <c r="S61" s="87"/>
     </row>
     <row r="62" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
@@ -5640,32 +5639,32 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="59" t="s">
+      <c r="C62" s="54" t="s">
+        <v>284</v>
+      </c>
+      <c r="D62" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="F62" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H62" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="D62" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="E62" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="F62" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="G62" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="H62" s="46" t="s">
-        <v>286</v>
-      </c>
       <c r="I62" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J62" s="46" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K62" s="46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L62" s="47">
         <v>1</v>
@@ -5677,18 +5676,18 @@
       <c r="N62" s="46">
         <v>20</v>
       </c>
-      <c r="O62" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P62" s="53">
+      <c r="O62" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P62" s="49">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="Q62" s="53">
+      <c r="Q62" s="49">
         <f t="shared" si="2"/>
         <v>0.42999999999999994</v>
       </c>
       <c r="R62" s="48"/>
-      <c r="S62" s="49"/>
+      <c r="S62" s="81"/>
     </row>
     <row r="63" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
@@ -5696,55 +5695,55 @@
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D63" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="F63" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="G63" s="50" t="s">
+      <c r="C63" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D63" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" s="84" t="s">
+        <v>131</v>
+      </c>
+      <c r="F63" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G63" s="83" t="s">
+        <v>408</v>
+      </c>
+      <c r="H63" s="83" t="s">
+        <v>286</v>
+      </c>
+      <c r="I63" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J63" s="83" t="s">
         <v>409</v>
       </c>
-      <c r="H63" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="I63" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J63" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="K63" s="50" t="s">
-        <v>333</v>
-      </c>
-      <c r="L63" s="51">
-        <v>1</v>
-      </c>
-      <c r="M63" s="50">
+      <c r="K63" s="83" t="s">
+        <v>332</v>
+      </c>
+      <c r="L63" s="84">
+        <v>1</v>
+      </c>
+      <c r="M63" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N63" s="50">
+      <c r="N63" s="83">
         <v>50</v>
       </c>
-      <c r="O63" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P63" s="54">
+      <c r="O63" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P63" s="86">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="Q63" s="54">
+      <c r="Q63" s="86">
         <f t="shared" si="2"/>
         <v>0.20500000000000002</v>
       </c>
-      <c r="R63" s="52"/>
-      <c r="S63" s="52"/>
+      <c r="R63" s="87"/>
+      <c r="S63" s="87"/>
     </row>
     <row r="64" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
@@ -5752,32 +5751,32 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="59" t="s">
-        <v>285</v>
+      <c r="C64" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F64" s="46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G64" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H64" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I64" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J64" s="46" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K64" s="46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L64" s="47">
         <v>1</v>
@@ -5789,18 +5788,18 @@
       <c r="N64" s="46">
         <v>100</v>
       </c>
-      <c r="O64" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P64" s="53">
+      <c r="O64" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P64" s="49">
         <v>1.9E-3</v>
       </c>
-      <c r="Q64" s="53">
+      <c r="Q64" s="49">
         <f t="shared" si="2"/>
         <v>0.19</v>
       </c>
       <c r="R64" s="48"/>
-      <c r="S64" s="49"/>
+      <c r="S64" s="81"/>
     </row>
     <row r="65" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
@@ -5808,55 +5807,55 @@
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D65" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="E65" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="F65" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="G65" s="50" t="s">
-        <v>238</v>
-      </c>
-      <c r="H65" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I65" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J65" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="K65" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="L65" s="51">
+      <c r="C65" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D65" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="84" t="s">
+        <v>133</v>
+      </c>
+      <c r="F65" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G65" s="83" t="s">
+        <v>237</v>
+      </c>
+      <c r="H65" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I65" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J65" s="83" t="s">
+        <v>412</v>
+      </c>
+      <c r="K65" s="83" t="s">
+        <v>334</v>
+      </c>
+      <c r="L65" s="84">
         <v>2</v>
       </c>
-      <c r="M65" s="50">
+      <c r="M65" s="83">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N65" s="50">
+      <c r="N65" s="83">
         <v>100</v>
       </c>
-      <c r="O65" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P65" s="54">
+      <c r="O65" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P65" s="86">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q65" s="54">
+      <c r="Q65" s="86">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="R65" s="52"/>
-      <c r="S65" s="52"/>
+      <c r="R65" s="87"/>
+      <c r="S65" s="87"/>
     </row>
     <row r="66" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
@@ -5864,32 +5863,32 @@
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="59" t="s">
-        <v>285</v>
+      <c r="C66" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F66" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G66" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I66" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J66" s="46" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K66" s="46" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L66" s="47">
         <v>1</v>
@@ -5901,18 +5900,18 @@
       <c r="N66" s="46">
         <v>20</v>
       </c>
-      <c r="O66" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P66" s="53">
+      <c r="O66" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P66" s="49">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="Q66" s="53">
+      <c r="Q66" s="49">
         <f t="shared" si="2"/>
         <v>0.76400000000000001</v>
       </c>
       <c r="R66" s="48"/>
-      <c r="S66" s="49"/>
+      <c r="S66" s="81"/>
     </row>
     <row r="67" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
@@ -5920,55 +5919,55 @@
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="D67" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="E67" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="F67" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="G67" s="50" t="s">
-        <v>240</v>
-      </c>
-      <c r="H67" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I67" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J67" s="50" t="s">
-        <v>414</v>
-      </c>
-      <c r="K67" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="L67" s="51">
-        <v>1</v>
-      </c>
-      <c r="M67" s="50">
+      <c r="C67" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="D67" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" s="84" t="s">
+        <v>135</v>
+      </c>
+      <c r="F67" s="83" t="s">
+        <v>179</v>
+      </c>
+      <c r="G67" s="83" t="s">
+        <v>239</v>
+      </c>
+      <c r="H67" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="I67" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J67" s="83" t="s">
+        <v>413</v>
+      </c>
+      <c r="K67" s="83" t="s">
+        <v>336</v>
+      </c>
+      <c r="L67" s="84">
+        <v>1</v>
+      </c>
+      <c r="M67" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N67" s="50">
+      <c r="N67" s="83">
         <v>100</v>
       </c>
-      <c r="O67" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P67" s="54">
+      <c r="O67" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P67" s="86">
         <v>1.4E-3</v>
       </c>
-      <c r="Q67" s="54">
+      <c r="Q67" s="86">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R67" s="52"/>
-      <c r="S67" s="52"/>
+      <c r="R67" s="87"/>
+      <c r="S67" s="87"/>
     </row>
     <row r="68" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -5976,32 +5975,32 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="59" t="s">
-        <v>285</v>
+      <c r="C68" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G68" s="47" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I68" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J68" s="46" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K68" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L68" s="47">
         <v>1</v>
@@ -6013,18 +6012,18 @@
       <c r="N68" s="46">
         <v>10</v>
       </c>
-      <c r="O68" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P68" s="53">
+      <c r="O68" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P68" s="49">
         <v>0.1487</v>
       </c>
-      <c r="Q68" s="53">
+      <c r="Q68" s="49">
         <f t="shared" si="2"/>
         <v>1.4870000000000001</v>
       </c>
       <c r="R68" s="48"/>
-      <c r="S68" s="49"/>
+      <c r="S68" s="81"/>
     </row>
     <row r="69" spans="1:19" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -6032,54 +6031,54 @@
         <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="60" t="s">
-        <v>183</v>
-      </c>
-      <c r="D69" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="E69" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="F69" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="G69" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="H69" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="I69" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J69" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="K69" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L69" s="51">
+      <c r="C69" s="82" t="s">
+        <v>182</v>
+      </c>
+      <c r="D69" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="E69" s="84" t="s">
+        <v>137</v>
+      </c>
+      <c r="F69" s="83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G69" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="H69" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="I69" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J69" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="K69" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L69" s="84">
         <v>38</v>
       </c>
-      <c r="M69" s="50">
+      <c r="M69" s="83">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="N69" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="O69" s="65" t="s">
-        <v>356</v>
-      </c>
-      <c r="P69" s="54" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q69" s="54" t="s">
-        <v>356</v>
-      </c>
-      <c r="R69" s="52"/>
-      <c r="S69" s="52"/>
+      <c r="N69" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="O69" s="85" t="s">
+        <v>355</v>
+      </c>
+      <c r="P69" s="86" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q69" s="86" t="s">
+        <v>355</v>
+      </c>
+      <c r="R69" s="87"/>
+      <c r="S69" s="87"/>
     </row>
     <row r="70" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
@@ -6087,32 +6086,32 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="59" t="s">
-        <v>352</v>
+      <c r="C70" s="54" t="s">
+        <v>351</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G70" s="47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H70" s="46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I70" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J70" s="46" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K70" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L70" s="47">
         <v>2</v>
@@ -6124,18 +6123,18 @@
       <c r="N70" s="46">
         <v>20</v>
       </c>
-      <c r="O70" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P70" s="53">
+      <c r="O70" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P70" s="49">
         <v>6.3E-2</v>
       </c>
-      <c r="Q70" s="53">
+      <c r="Q70" s="49">
         <f t="shared" si="2"/>
         <v>1.26</v>
       </c>
       <c r="R70" s="48"/>
-      <c r="S70" s="49"/>
+      <c r="S70" s="81"/>
     </row>
     <row r="71" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
@@ -6143,113 +6142,113 @@
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="60" t="s">
-        <v>353</v>
-      </c>
-      <c r="D71" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="E71" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="F71" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="G71" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="H71" s="50" t="s">
-        <v>278</v>
-      </c>
-      <c r="I71" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J71" s="50" t="s">
-        <v>417</v>
-      </c>
-      <c r="K71" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L71" s="51">
-        <v>1</v>
-      </c>
-      <c r="M71" s="50">
+      <c r="C71" s="82" t="s">
+        <v>352</v>
+      </c>
+      <c r="D71" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="84" t="s">
+        <v>139</v>
+      </c>
+      <c r="F71" s="83" t="s">
+        <v>184</v>
+      </c>
+      <c r="G71" s="83" t="s">
+        <v>240</v>
+      </c>
+      <c r="H71" s="83" t="s">
+        <v>277</v>
+      </c>
+      <c r="I71" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J71" s="83" t="s">
+        <v>416</v>
+      </c>
+      <c r="K71" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L71" s="84">
+        <v>1</v>
+      </c>
+      <c r="M71" s="83">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N71" s="50">
+      <c r="N71" s="83">
         <v>6</v>
       </c>
-      <c r="O71" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P71" s="54">
+      <c r="O71" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P71" s="86">
         <v>0.49059999999999998</v>
       </c>
-      <c r="Q71" s="54">
+      <c r="Q71" s="86">
         <f t="shared" si="2"/>
         <v>2.9436</v>
       </c>
-      <c r="R71" s="52"/>
-      <c r="S71" s="52"/>
-    </row>
-    <row r="72" spans="1:19" s="88" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="80"/>
-      <c r="B72" s="81">
+      <c r="R71" s="87"/>
+      <c r="S71" s="87"/>
+    </row>
+    <row r="72" spans="1:19" s="70" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="62"/>
+      <c r="B72" s="63">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="82" t="s">
-        <v>353</v>
-      </c>
-      <c r="D72" s="83" t="s">
-        <v>66</v>
-      </c>
-      <c r="E72" s="84" t="s">
-        <v>141</v>
-      </c>
-      <c r="F72" s="83" t="s">
-        <v>186</v>
-      </c>
-      <c r="G72" s="84" t="s">
-        <v>242</v>
-      </c>
-      <c r="H72" s="83" t="s">
-        <v>290</v>
-      </c>
-      <c r="I72" s="83" t="s">
-        <v>356</v>
-      </c>
-      <c r="J72" s="83" t="s">
-        <v>356</v>
-      </c>
-      <c r="K72" s="83" t="s">
-        <v>356</v>
-      </c>
-      <c r="L72" s="84">
-        <v>1</v>
-      </c>
-      <c r="M72" s="83">
+      <c r="C72" s="64" t="s">
+        <v>352</v>
+      </c>
+      <c r="D72" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="E72" s="66" t="s">
+        <v>140</v>
+      </c>
+      <c r="F72" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="G72" s="66" t="s">
+        <v>241</v>
+      </c>
+      <c r="H72" s="65" t="s">
+        <v>289</v>
+      </c>
+      <c r="I72" s="65" t="s">
+        <v>355</v>
+      </c>
+      <c r="J72" s="65" t="s">
+        <v>355</v>
+      </c>
+      <c r="K72" s="65" t="s">
+        <v>355</v>
+      </c>
+      <c r="L72" s="66">
+        <v>1</v>
+      </c>
+      <c r="M72" s="65">
         <f t="shared" ref="M72:M84" si="3">L72*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="83">
+      <c r="N72" s="65">
         <v>6</v>
       </c>
-      <c r="O72" s="85" t="s">
-        <v>454</v>
-      </c>
-      <c r="P72" s="86">
+      <c r="O72" s="67" t="s">
+        <v>453</v>
+      </c>
+      <c r="P72" s="68">
         <v>10.87</v>
       </c>
-      <c r="Q72" s="86">
+      <c r="Q72" s="68">
         <f t="shared" ref="Q72:Q84" si="4">P72*N72</f>
         <v>65.22</v>
       </c>
-      <c r="R72" s="87" t="s">
-        <v>453</v>
-      </c>
-      <c r="S72" s="49"/>
+      <c r="R72" s="69" t="s">
+        <v>452</v>
+      </c>
+      <c r="S72" s="81"/>
     </row>
     <row r="73" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
@@ -6257,55 +6256,55 @@
         <f>ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
-      <c r="C73" s="60" t="s">
-        <v>353</v>
-      </c>
-      <c r="D73" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="E73" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="F73" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="G73" s="50" t="s">
-        <v>243</v>
-      </c>
-      <c r="H73" s="50" t="s">
-        <v>279</v>
-      </c>
-      <c r="I73" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J73" s="50" t="s">
-        <v>418</v>
-      </c>
-      <c r="K73" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L73" s="51">
+      <c r="C73" s="82" t="s">
+        <v>352</v>
+      </c>
+      <c r="D73" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="E73" s="84" t="s">
+        <v>141</v>
+      </c>
+      <c r="F73" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="G73" s="83" t="s">
+        <v>242</v>
+      </c>
+      <c r="H73" s="83" t="s">
+        <v>278</v>
+      </c>
+      <c r="I73" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J73" s="83" t="s">
+        <v>417</v>
+      </c>
+      <c r="K73" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L73" s="84">
         <v>2</v>
       </c>
-      <c r="M73" s="50">
+      <c r="M73" s="83">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N73" s="50">
+      <c r="N73" s="83">
         <v>11</v>
       </c>
-      <c r="O73" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P73" s="54">
+      <c r="O73" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P73" s="86">
         <v>0.79530000000000001</v>
       </c>
-      <c r="Q73" s="54">
+      <c r="Q73" s="86">
         <f t="shared" si="4"/>
         <v>8.7483000000000004</v>
       </c>
-      <c r="R73" s="52"/>
-      <c r="S73" s="52"/>
+      <c r="R73" s="87"/>
+      <c r="S73" s="87"/>
     </row>
     <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -6313,32 +6312,32 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="59" t="s">
-        <v>353</v>
+      <c r="C74" s="54" t="s">
+        <v>352</v>
       </c>
       <c r="D74" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E74" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G74" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H74" s="46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I74" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J74" s="46" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K74" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L74" s="47">
         <v>1</v>
@@ -6350,18 +6349,18 @@
       <c r="N74" s="46">
         <v>6</v>
       </c>
-      <c r="O74" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P74" s="53">
+      <c r="O74" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P74" s="49">
         <v>0.38390000000000002</v>
       </c>
-      <c r="Q74" s="53">
+      <c r="Q74" s="49">
         <f t="shared" si="4"/>
         <v>2.3033999999999999</v>
       </c>
       <c r="R74" s="48"/>
-      <c r="S74" s="49"/>
+      <c r="S74" s="81"/>
     </row>
     <row r="75" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
@@ -6369,55 +6368,55 @@
         <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="60" t="s">
-        <v>353</v>
-      </c>
-      <c r="D75" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="E75" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="F75" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="G75" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="H75" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="I75" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J75" s="50" t="s">
-        <v>419</v>
-      </c>
-      <c r="K75" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L75" s="51">
-        <v>1</v>
-      </c>
-      <c r="M75" s="50">
+      <c r="C75" s="82" t="s">
+        <v>352</v>
+      </c>
+      <c r="D75" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="E75" s="84" t="s">
+        <v>143</v>
+      </c>
+      <c r="F75" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="G75" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="H75" s="83" t="s">
+        <v>290</v>
+      </c>
+      <c r="I75" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J75" s="83" t="s">
+        <v>418</v>
+      </c>
+      <c r="K75" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L75" s="84">
+        <v>1</v>
+      </c>
+      <c r="M75" s="83">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N75" s="50">
+      <c r="N75" s="83">
         <v>6</v>
       </c>
-      <c r="O75" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P75" s="54">
+      <c r="O75" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P75" s="86">
         <v>2.5665</v>
       </c>
-      <c r="Q75" s="54">
+      <c r="Q75" s="86">
         <f t="shared" si="4"/>
         <v>15.399000000000001</v>
       </c>
-      <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
+      <c r="R75" s="87"/>
+      <c r="S75" s="87"/>
     </row>
     <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
@@ -6425,32 +6424,32 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C76" s="59" t="s">
-        <v>353</v>
+      <c r="C76" s="54" t="s">
+        <v>352</v>
       </c>
       <c r="D76" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E76" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G76" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I76" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L76" s="47">
         <v>1</v>
@@ -6462,20 +6461,20 @@
       <c r="N76" s="46">
         <v>6</v>
       </c>
-      <c r="O76" s="64" t="s">
-        <v>454</v>
-      </c>
-      <c r="P76" s="53">
+      <c r="O76" s="58" t="s">
+        <v>453</v>
+      </c>
+      <c r="P76" s="49">
         <v>43.5</v>
       </c>
-      <c r="Q76" s="53">
+      <c r="Q76" s="49">
         <f t="shared" si="4"/>
         <v>261</v>
       </c>
-      <c r="R76" s="87" t="s">
-        <v>453</v>
-      </c>
-      <c r="S76" s="49"/>
+      <c r="R76" s="69" t="s">
+        <v>452</v>
+      </c>
+      <c r="S76" s="81"/>
     </row>
     <row r="77" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
@@ -6483,55 +6482,55 @@
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="60" t="s">
-        <v>353</v>
-      </c>
-      <c r="D77" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="E77" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="F77" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="G77" s="50" t="s">
-        <v>247</v>
-      </c>
-      <c r="H77" s="50" t="s">
-        <v>293</v>
-      </c>
-      <c r="I77" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J77" s="50" t="s">
-        <v>421</v>
-      </c>
-      <c r="K77" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L77" s="51">
-        <v>1</v>
-      </c>
-      <c r="M77" s="50">
+      <c r="C77" s="82" t="s">
+        <v>352</v>
+      </c>
+      <c r="D77" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="E77" s="84" t="s">
+        <v>145</v>
+      </c>
+      <c r="F77" s="83" t="s">
+        <v>188</v>
+      </c>
+      <c r="G77" s="83" t="s">
+        <v>246</v>
+      </c>
+      <c r="H77" s="83" t="s">
+        <v>292</v>
+      </c>
+      <c r="I77" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J77" s="83" t="s">
+        <v>420</v>
+      </c>
+      <c r="K77" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L77" s="84">
+        <v>1</v>
+      </c>
+      <c r="M77" s="83">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N77" s="50">
+      <c r="N77" s="83">
         <v>6</v>
       </c>
-      <c r="O77" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P77" s="54">
+      <c r="O77" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P77" s="86">
         <v>0.76259999999999994</v>
       </c>
-      <c r="Q77" s="54">
+      <c r="Q77" s="86">
         <f t="shared" si="4"/>
         <v>4.5755999999999997</v>
       </c>
-      <c r="R77" s="52"/>
-      <c r="S77" s="52"/>
+      <c r="R77" s="87"/>
+      <c r="S77" s="87"/>
     </row>
     <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -6539,32 +6538,32 @@
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="59" t="s">
-        <v>353</v>
+      <c r="C78" s="54" t="s">
+        <v>352</v>
       </c>
       <c r="D78" s="46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F78" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H78" s="46" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I78" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J78" s="46" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K78" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L78" s="47">
         <v>1</v>
@@ -6576,18 +6575,18 @@
       <c r="N78" s="46">
         <v>6</v>
       </c>
-      <c r="O78" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P78" s="53">
+      <c r="O78" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P78" s="49">
         <v>4.2103999999999999</v>
       </c>
-      <c r="Q78" s="53">
+      <c r="Q78" s="49">
         <f t="shared" si="4"/>
         <v>25.2624</v>
       </c>
       <c r="R78" s="48"/>
-      <c r="S78" s="49"/>
+      <c r="S78" s="81"/>
     </row>
     <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -6595,55 +6594,55 @@
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="60" t="s">
-        <v>353</v>
-      </c>
-      <c r="D79" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="E79" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="F79" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="G79" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="H79" s="50" t="s">
-        <v>295</v>
-      </c>
-      <c r="I79" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J79" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="K79" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L79" s="51">
-        <v>1</v>
-      </c>
-      <c r="M79" s="50">
+      <c r="C79" s="82" t="s">
+        <v>352</v>
+      </c>
+      <c r="D79" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="E79" s="84" t="s">
+        <v>147</v>
+      </c>
+      <c r="F79" s="83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G79" s="83" t="s">
+        <v>190</v>
+      </c>
+      <c r="H79" s="83" t="s">
+        <v>294</v>
+      </c>
+      <c r="I79" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J79" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="K79" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L79" s="84">
+        <v>1</v>
+      </c>
+      <c r="M79" s="83">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N79" s="50">
+      <c r="N79" s="83">
         <v>6</v>
       </c>
-      <c r="O79" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P79" s="54">
+      <c r="O79" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P79" s="86">
         <v>1.4825999999999999</v>
       </c>
-      <c r="Q79" s="54">
+      <c r="Q79" s="86">
         <f t="shared" si="4"/>
         <v>8.8956</v>
       </c>
-      <c r="R79" s="52"/>
-      <c r="S79" s="52"/>
+      <c r="R79" s="87"/>
+      <c r="S79" s="87"/>
     </row>
     <row r="80" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
@@ -6651,32 +6650,32 @@
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C80" s="59" t="s">
-        <v>353</v>
+      <c r="C80" s="54" t="s">
+        <v>352</v>
       </c>
       <c r="D80" s="46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E80" s="47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F80" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G80" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H80" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I80" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J80" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K80" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L80" s="47">
         <v>1</v>
@@ -6688,20 +6687,20 @@
       <c r="N80" s="46">
         <v>6</v>
       </c>
-      <c r="O80" s="64" t="s">
-        <v>454</v>
-      </c>
-      <c r="P80" s="53">
+      <c r="O80" s="58" t="s">
+        <v>453</v>
+      </c>
+      <c r="P80" s="49">
         <v>3.2</v>
       </c>
-      <c r="Q80" s="53">
+      <c r="Q80" s="49">
         <f t="shared" si="4"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="R80" s="87" t="s">
-        <v>453</v>
-      </c>
-      <c r="S80" s="49"/>
+      <c r="R80" s="69" t="s">
+        <v>452</v>
+      </c>
+      <c r="S80" s="81"/>
     </row>
     <row r="81" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
@@ -6709,55 +6708,55 @@
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="60" t="s">
-        <v>353</v>
-      </c>
-      <c r="D81" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="E81" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="F81" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="G81" s="50" t="s">
-        <v>250</v>
-      </c>
-      <c r="H81" s="50" t="s">
-        <v>296</v>
-      </c>
-      <c r="I81" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J81" s="50" t="s">
-        <v>424</v>
-      </c>
-      <c r="K81" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L81" s="51">
-        <v>1</v>
-      </c>
-      <c r="M81" s="50">
+      <c r="C81" s="82" t="s">
+        <v>352</v>
+      </c>
+      <c r="D81" s="83" t="s">
+        <v>74</v>
+      </c>
+      <c r="E81" s="84" t="s">
+        <v>149</v>
+      </c>
+      <c r="F81" s="83" t="s">
+        <v>191</v>
+      </c>
+      <c r="G81" s="83" t="s">
+        <v>249</v>
+      </c>
+      <c r="H81" s="83" t="s">
+        <v>295</v>
+      </c>
+      <c r="I81" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J81" s="83" t="s">
+        <v>423</v>
+      </c>
+      <c r="K81" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L81" s="84">
+        <v>1</v>
+      </c>
+      <c r="M81" s="83">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N81" s="50">
+      <c r="N81" s="83">
         <v>6</v>
       </c>
-      <c r="O81" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P81" s="54">
+      <c r="O81" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P81" s="86">
         <v>0.49230000000000002</v>
       </c>
-      <c r="Q81" s="54">
+      <c r="Q81" s="86">
         <f t="shared" si="4"/>
         <v>2.9538000000000002</v>
       </c>
-      <c r="R81" s="52"/>
-      <c r="S81" s="52"/>
+      <c r="R81" s="87"/>
+      <c r="S81" s="87"/>
     </row>
     <row r="82" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
@@ -6765,32 +6764,32 @@
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C82" s="59" t="s">
-        <v>353</v>
+      <c r="C82" s="54" t="s">
+        <v>352</v>
       </c>
       <c r="D82" s="46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F82" s="46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G82" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H82" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I82" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J82" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K82" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L82" s="47">
         <v>1</v>
@@ -6802,20 +6801,20 @@
       <c r="N82" s="46">
         <v>6</v>
       </c>
-      <c r="O82" s="64" t="s">
-        <v>454</v>
-      </c>
-      <c r="P82" s="53">
+      <c r="O82" s="58" t="s">
+        <v>453</v>
+      </c>
+      <c r="P82" s="49">
         <v>1.45</v>
       </c>
-      <c r="Q82" s="53">
+      <c r="Q82" s="49">
         <f t="shared" si="4"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="R82" s="87" t="s">
-        <v>453</v>
-      </c>
-      <c r="S82" s="49"/>
+      <c r="R82" s="69" t="s">
+        <v>452</v>
+      </c>
+      <c r="S82" s="81"/>
     </row>
     <row r="83" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
@@ -6823,55 +6822,55 @@
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="60" t="s">
+      <c r="C83" s="82" t="s">
+        <v>353</v>
+      </c>
+      <c r="D83" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="E83" s="84" t="s">
+        <v>151</v>
+      </c>
+      <c r="F83" s="83" t="s">
         <v>354</v>
       </c>
-      <c r="D83" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="E83" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="F83" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="G83" s="50" t="s">
-        <v>193</v>
-      </c>
-      <c r="H83" s="50" t="s">
-        <v>298</v>
-      </c>
-      <c r="I83" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="J83" s="50" t="s">
-        <v>425</v>
-      </c>
-      <c r="K83" s="50" t="s">
-        <v>338</v>
-      </c>
-      <c r="L83" s="51">
-        <v>1</v>
-      </c>
-      <c r="M83" s="50">
+      <c r="G83" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="H83" s="83" t="s">
+        <v>297</v>
+      </c>
+      <c r="I83" s="83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J83" s="83" t="s">
+        <v>424</v>
+      </c>
+      <c r="K83" s="83" t="s">
+        <v>337</v>
+      </c>
+      <c r="L83" s="84">
+        <v>1</v>
+      </c>
+      <c r="M83" s="83">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N83" s="50">
+      <c r="N83" s="83">
         <v>10</v>
       </c>
-      <c r="O83" s="65" t="s">
-        <v>369</v>
-      </c>
-      <c r="P83" s="54">
+      <c r="O83" s="85" t="s">
+        <v>368</v>
+      </c>
+      <c r="P83" s="86">
         <v>8.6900000000000005E-2</v>
       </c>
-      <c r="Q83" s="54">
+      <c r="Q83" s="86">
         <f t="shared" si="4"/>
         <v>0.86899999999999999</v>
       </c>
-      <c r="R83" s="52"/>
-      <c r="S83" s="52"/>
+      <c r="R83" s="87"/>
+      <c r="S83" s="87"/>
     </row>
     <row r="84" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
@@ -6879,32 +6878,32 @@
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C84" s="59" t="s">
+      <c r="C84" s="54" t="s">
+        <v>353</v>
+      </c>
+      <c r="D84" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="E84" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="F84" s="46" t="s">
         <v>354</v>
       </c>
-      <c r="D84" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="E84" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="F84" s="46" t="s">
-        <v>355</v>
-      </c>
       <c r="G84" s="47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H84" s="46" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I84" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J84" s="46" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K84" s="46" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L84" s="47">
         <v>1</v>
@@ -6916,18 +6915,18 @@
       <c r="N84" s="46">
         <v>10</v>
       </c>
-      <c r="O84" s="64" t="s">
-        <v>369</v>
-      </c>
-      <c r="P84" s="53">
+      <c r="O84" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="P84" s="49">
         <v>0.112</v>
       </c>
-      <c r="Q84" s="53">
+      <c r="Q84" s="49">
         <f t="shared" si="4"/>
         <v>1.1200000000000001</v>
       </c>
       <c r="R84" s="48"/>
-      <c r="S84" s="49"/>
+      <c r="S84" s="81"/>
     </row>
     <row r="85" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
@@ -6943,17 +6942,17 @@
       <c r="K85" s="37"/>
       <c r="L85" s="37"/>
       <c r="M85" s="37"/>
-      <c r="N85" s="78" t="s">
-        <v>449</v>
-      </c>
-      <c r="O85" s="79"/>
-      <c r="P85" s="79"/>
-      <c r="Q85" s="68">
+      <c r="N85" s="79" t="s">
+        <v>448</v>
+      </c>
+      <c r="O85" s="80"/>
+      <c r="P85" s="80"/>
+      <c r="Q85" s="60">
         <f>SUM(Q10:Q84)</f>
         <v>510.77860000000004</v>
       </c>
-      <c r="R85" s="74"/>
-      <c r="S85" s="75"/>
+      <c r="R85" s="75"/>
+      <c r="S85" s="76"/>
     </row>
     <row r="86" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
@@ -6969,17 +6968,17 @@
       <c r="K86" s="10"/>
       <c r="L86" s="10"/>
       <c r="M86" s="10"/>
-      <c r="N86" s="78" t="s">
-        <v>450</v>
-      </c>
-      <c r="O86" s="79"/>
-      <c r="P86" s="79"/>
-      <c r="Q86" s="69">
+      <c r="N86" s="79" t="s">
+        <v>449</v>
+      </c>
+      <c r="O86" s="80"/>
+      <c r="P86" s="80"/>
+      <c r="Q86" s="61">
         <f>Q85/5</f>
         <v>102.15572</v>
       </c>
-      <c r="R86" s="76"/>
-      <c r="S86" s="77"/>
+      <c r="R86" s="77"/>
+      <c r="S86" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6990,74 +6989,74 @@
     <mergeCell ref="N86:P86"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{FFDF232B-BF83-4687-9D10-930C81570C73}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{DA1DE63F-4359-464E-947B-0FD6A55C6AFC}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{B9F9B852-E96F-4ACD-AF52-F62865344352}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{0ABB5F52-C97E-4A95-921C-0DBA9F071AB0}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{D1C66806-C117-43FC-A89C-D37ED5E95C19}"/>
-    <hyperlink ref="O15" r:id="rId6" xr:uid="{1131A422-8500-43CE-A804-D7906C69967E}"/>
-    <hyperlink ref="O16" r:id="rId7" xr:uid="{F19F0AC8-C0E5-4A13-969A-75D21B427BB0}"/>
-    <hyperlink ref="O17" r:id="rId8" xr:uid="{F21DEF5C-D491-4F8E-8540-3A90974260B0}"/>
-    <hyperlink ref="O18" r:id="rId9" xr:uid="{F945B7A2-A06A-41F9-802A-3525FA0CBF66}"/>
-    <hyperlink ref="O19" r:id="rId10" xr:uid="{ED06BC52-68B2-4AE0-B2D2-00CBE22953C6}"/>
-    <hyperlink ref="O20" r:id="rId11" xr:uid="{DDC0221E-ED6D-4559-926A-9D819F258397}"/>
-    <hyperlink ref="O21" r:id="rId12" xr:uid="{54941123-B2AC-4DD7-BCFB-90C36B226586}"/>
-    <hyperlink ref="O23" r:id="rId13" xr:uid="{3A5EE74A-B6F8-40A6-BD4B-89BA178EB81B}"/>
-    <hyperlink ref="O25" r:id="rId14" xr:uid="{11584FA5-032C-4DBF-9765-23C07BFCAEF8}"/>
-    <hyperlink ref="O30" r:id="rId15" xr:uid="{5EE103CF-C83D-4586-9E7F-96A1AEFD992F}"/>
-    <hyperlink ref="O33" r:id="rId16" xr:uid="{9BD9D495-5645-4172-B487-110252732D05}"/>
-    <hyperlink ref="O34" r:id="rId17" xr:uid="{25BC95A3-A7EB-4F4C-8609-ACEF5B806297}"/>
-    <hyperlink ref="O35" r:id="rId18" xr:uid="{B8C65A29-D9CC-4E85-B5F1-306F35036E2B}"/>
-    <hyperlink ref="O36" r:id="rId19" xr:uid="{5A65F15C-5469-4C4D-BB38-90C0641F63DF}"/>
-    <hyperlink ref="O37" r:id="rId20" xr:uid="{DC54B3AF-08D1-46BA-A8A7-3995C1DF2DED}"/>
-    <hyperlink ref="O40" r:id="rId21" xr:uid="{DD3949ED-3BA9-4834-9562-801D5FD6DF91}"/>
-    <hyperlink ref="O42" r:id="rId22" xr:uid="{969558E3-B81A-42B2-A615-8543AB4C5552}"/>
-    <hyperlink ref="O45" r:id="rId23" xr:uid="{40957DD9-6F9F-4B6D-AB9C-2BB21C83C065}"/>
-    <hyperlink ref="O46" r:id="rId24" xr:uid="{9BD4C9D3-40E8-4ADF-B16B-8E4F58DB9CD4}"/>
-    <hyperlink ref="O47" r:id="rId25" xr:uid="{D66C022A-9469-4448-9F7B-02AE7A377015}"/>
-    <hyperlink ref="O48" r:id="rId26" xr:uid="{B7504B37-B01A-485F-82B4-B682BACA56F4}"/>
-    <hyperlink ref="O49" r:id="rId27" xr:uid="{FDA89C7D-3DF3-4831-BAAE-6C44881FCC8B}"/>
-    <hyperlink ref="O50" r:id="rId28" xr:uid="{40FA51F4-73EA-4E29-8591-4648718DA037}"/>
-    <hyperlink ref="O51" r:id="rId29" xr:uid="{EC238B24-0256-4C29-AE21-78404FA26592}"/>
-    <hyperlink ref="O52" r:id="rId30" xr:uid="{6335071D-AE40-48DA-A13C-9B8B9AD4D7C0}"/>
-    <hyperlink ref="O54" r:id="rId31" xr:uid="{5ED418C2-581E-4000-9F7C-7BC6D173B7EF}"/>
-    <hyperlink ref="O55" r:id="rId32" xr:uid="{D7F533A6-81AC-417E-9AA8-894901942B06}"/>
-    <hyperlink ref="O56" r:id="rId33" xr:uid="{3C7C3E89-1710-4BA6-8D0A-291B0F44D5C6}"/>
-    <hyperlink ref="O57" r:id="rId34" xr:uid="{7D792518-01CA-48DC-AE86-544C4AF4C5FD}"/>
-    <hyperlink ref="O58" r:id="rId35" xr:uid="{C244C886-3C06-42B4-877D-80056E64A473}"/>
-    <hyperlink ref="O59" r:id="rId36" xr:uid="{74AB7B1D-C0F6-4F8E-A993-4B4DD7841A5B}"/>
-    <hyperlink ref="O60" r:id="rId37" xr:uid="{3E71446B-708C-47F0-BEDB-F4A9A3CA5ACF}"/>
-    <hyperlink ref="O61" r:id="rId38" xr:uid="{A2A93AFD-247B-441A-83A7-846D175F5244}"/>
-    <hyperlink ref="O62" r:id="rId39" xr:uid="{BA6C9F4A-EEAD-42CD-AC5F-22864A0F3840}"/>
-    <hyperlink ref="O63" r:id="rId40" xr:uid="{62F0F06D-ABB0-40A1-A2EB-ABFD1853F5D5}"/>
-    <hyperlink ref="O64" r:id="rId41" xr:uid="{4636F4B8-0DF0-4D7D-95B9-3494C56B8336}"/>
-    <hyperlink ref="O65" r:id="rId42" xr:uid="{F6A957DB-D8D6-425B-B9DD-0F7F68BFD04F}"/>
-    <hyperlink ref="O66" r:id="rId43" xr:uid="{73BD8A20-F2C7-407B-BCFD-E618FCEE7BD1}"/>
-    <hyperlink ref="O67" r:id="rId44" xr:uid="{21B0DA1B-6E5B-4362-9C10-6D968A37D8D5}"/>
-    <hyperlink ref="O68" r:id="rId45" xr:uid="{F499B213-D8E5-4209-BFA9-5CFCAE3D237B}"/>
-    <hyperlink ref="O70" r:id="rId46" xr:uid="{5DD60496-557D-46E8-9F11-37BB44D81837}"/>
-    <hyperlink ref="O71" r:id="rId47" xr:uid="{519227CC-3426-4F60-A9EE-34DA056C7F55}"/>
-    <hyperlink ref="O73" r:id="rId48" xr:uid="{E405F7D4-4F6F-4EC3-B126-A00C50709986}"/>
-    <hyperlink ref="O75" r:id="rId49" xr:uid="{29D2ED58-A2E0-40F3-99CE-B4C2CA638EB6}"/>
-    <hyperlink ref="O74" r:id="rId50" xr:uid="{CAE47FAD-CCF6-49F4-8495-FF9C044317FB}"/>
-    <hyperlink ref="O77" r:id="rId51" xr:uid="{AC164C7C-CACA-44D3-9738-72415302B728}"/>
-    <hyperlink ref="O78" r:id="rId52" xr:uid="{8231F02D-A710-43A7-B966-BCE939C43506}"/>
-    <hyperlink ref="O79" r:id="rId53" xr:uid="{65F2D221-E890-45D3-B859-0DF47EE540F2}"/>
-    <hyperlink ref="O81" r:id="rId54" xr:uid="{89D001BA-46B9-49D7-A308-A27240FB5F98}"/>
-    <hyperlink ref="O83" r:id="rId55" xr:uid="{2F3A0847-F001-4D8A-A2CB-2DC095CC24CC}"/>
-    <hyperlink ref="O84" r:id="rId56" xr:uid="{F8B55971-530A-4189-B312-D772FB4CA69B}"/>
-    <hyperlink ref="O22" r:id="rId57" xr:uid="{266C89ED-C124-47E2-84B3-4A01BD69A504}"/>
-    <hyperlink ref="O24" r:id="rId58" xr:uid="{F865C2CC-EE07-4B5F-8008-E1A205DE005A}"/>
-    <hyperlink ref="O26" r:id="rId59" xr:uid="{4DB77D3D-7151-46E4-9281-78BB782CB9AD}"/>
-    <hyperlink ref="O27" r:id="rId60" xr:uid="{4755A196-86D6-427B-9073-A496CE2A40C0}"/>
-    <hyperlink ref="O28" r:id="rId61" xr:uid="{1252FBC2-F125-449D-B287-D62053C0FAE4}"/>
-    <hyperlink ref="O29" r:id="rId62" xr:uid="{D87F2853-43EC-425A-A8CC-5B8A66E228FE}"/>
-    <hyperlink ref="O31" r:id="rId63" xr:uid="{63F57488-A175-4233-9B21-838164228F70}"/>
-    <hyperlink ref="O32" r:id="rId64" xr:uid="{BFF0A1CE-8710-48BB-BFE0-A6747A325933}"/>
-    <hyperlink ref="O39" r:id="rId65" xr:uid="{89BFF0F6-3AA1-43B9-9D5B-8332336B9E80}"/>
-    <hyperlink ref="O38" r:id="rId66" xr:uid="{EFAE510A-8D53-4113-9D1D-3505C217C37C}"/>
-    <hyperlink ref="O41" r:id="rId67" xr:uid="{FC1DE3C3-D166-422F-A178-C2F2BDF752FF}"/>
-    <hyperlink ref="O43" r:id="rId68" xr:uid="{6F25AA1F-2B1D-4202-ACEB-84BEE3608EB1}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O15" r:id="rId6"/>
+    <hyperlink ref="O16" r:id="rId7"/>
+    <hyperlink ref="O17" r:id="rId8"/>
+    <hyperlink ref="O18" r:id="rId9"/>
+    <hyperlink ref="O19" r:id="rId10"/>
+    <hyperlink ref="O20" r:id="rId11"/>
+    <hyperlink ref="O21" r:id="rId12"/>
+    <hyperlink ref="O23" r:id="rId13"/>
+    <hyperlink ref="O25" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O33" r:id="rId16"/>
+    <hyperlink ref="O34" r:id="rId17"/>
+    <hyperlink ref="O35" r:id="rId18"/>
+    <hyperlink ref="O36" r:id="rId19"/>
+    <hyperlink ref="O37" r:id="rId20"/>
+    <hyperlink ref="O40" r:id="rId21"/>
+    <hyperlink ref="O42" r:id="rId22"/>
+    <hyperlink ref="O45" r:id="rId23"/>
+    <hyperlink ref="O46" r:id="rId24"/>
+    <hyperlink ref="O47" r:id="rId25"/>
+    <hyperlink ref="O48" r:id="rId26"/>
+    <hyperlink ref="O49" r:id="rId27"/>
+    <hyperlink ref="O50" r:id="rId28"/>
+    <hyperlink ref="O51" r:id="rId29"/>
+    <hyperlink ref="O52" r:id="rId30"/>
+    <hyperlink ref="O54" r:id="rId31"/>
+    <hyperlink ref="O55" r:id="rId32"/>
+    <hyperlink ref="O56" r:id="rId33"/>
+    <hyperlink ref="O57" r:id="rId34"/>
+    <hyperlink ref="O58" r:id="rId35"/>
+    <hyperlink ref="O59" r:id="rId36"/>
+    <hyperlink ref="O60" r:id="rId37"/>
+    <hyperlink ref="O61" r:id="rId38"/>
+    <hyperlink ref="O62" r:id="rId39"/>
+    <hyperlink ref="O63" r:id="rId40"/>
+    <hyperlink ref="O64" r:id="rId41"/>
+    <hyperlink ref="O65" r:id="rId42"/>
+    <hyperlink ref="O66" r:id="rId43"/>
+    <hyperlink ref="O67" r:id="rId44"/>
+    <hyperlink ref="O68" r:id="rId45"/>
+    <hyperlink ref="O70" r:id="rId46"/>
+    <hyperlink ref="O71" r:id="rId47"/>
+    <hyperlink ref="O73" r:id="rId48"/>
+    <hyperlink ref="O75" r:id="rId49"/>
+    <hyperlink ref="O74" r:id="rId50"/>
+    <hyperlink ref="O77" r:id="rId51"/>
+    <hyperlink ref="O78" r:id="rId52"/>
+    <hyperlink ref="O79" r:id="rId53"/>
+    <hyperlink ref="O81" r:id="rId54"/>
+    <hyperlink ref="O83" r:id="rId55"/>
+    <hyperlink ref="O84" r:id="rId56"/>
+    <hyperlink ref="O22" r:id="rId57"/>
+    <hyperlink ref="O24" r:id="rId58"/>
+    <hyperlink ref="O26" r:id="rId59"/>
+    <hyperlink ref="O27" r:id="rId60"/>
+    <hyperlink ref="O28" r:id="rId61"/>
+    <hyperlink ref="O29" r:id="rId62"/>
+    <hyperlink ref="O31" r:id="rId63"/>
+    <hyperlink ref="O32" r:id="rId64"/>
+    <hyperlink ref="O39" r:id="rId65"/>
+    <hyperlink ref="O38" r:id="rId66"/>
+    <hyperlink ref="O41" r:id="rId67"/>
+    <hyperlink ref="O43" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId69"/>
@@ -7066,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8056F525-F359-4DA6-9DFA-4BD0112C86EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7075,630 +7074,630 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="61" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="62" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="62">
+      <c r="C5" s="56">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="56"/>
+      <c r="C7" s="56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="57">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="63">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="56">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="62">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="62"/>
-      <c r="C7" s="62">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="56">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="63" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="63">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="56" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="56">
+        <v>61300611121</v>
+      </c>
+      <c r="C37" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="C38" s="57">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="62" t="s">
-        <v>198</v>
-      </c>
-      <c r="C9" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="63" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="63">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40" s="57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="C42" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="C43" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="C44" s="57">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="62" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="63" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" s="63">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="C45" s="56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" s="56">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="C48" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="C49" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="C50" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="C51" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="C52" s="57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="C53" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="57" t="s">
+        <v>231</v>
+      </c>
+      <c r="C54" s="57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="C55" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="C56" s="57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="C57" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="C58" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="56"/>
+      <c r="C59" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="C60" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="56" t="s">
+        <v>237</v>
+      </c>
+      <c r="C61" s="56">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="62" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="62">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="C63" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="C64" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="56" t="s">
+        <v>182</v>
+      </c>
+      <c r="C65" s="56">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="57" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" s="57">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="C16" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="C17" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="63" t="s">
-        <v>207</v>
-      </c>
-      <c r="C18" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="62">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="C20" s="63">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="62" t="s">
-        <v>210</v>
-      </c>
-      <c r="C21" s="62">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="62" t="s">
-        <v>211</v>
-      </c>
-      <c r="C23" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="63" t="s">
-        <v>212</v>
-      </c>
-      <c r="C24" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="63" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="C27" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="63" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="62" t="s">
-        <v>167</v>
-      </c>
-      <c r="C29" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="63" t="s">
-        <v>214</v>
-      </c>
-      <c r="C30" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="C32" s="63">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="62" t="s">
-        <v>217</v>
-      </c>
-      <c r="C33" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="C34" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="C35" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="63" t="s">
-        <v>173</v>
-      </c>
-      <c r="C36" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="62">
-        <v>61300611121</v>
-      </c>
-      <c r="C37" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="63" t="s">
-        <v>356</v>
-      </c>
-      <c r="C38" s="63">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="C67" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="C68" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="56" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69" s="56">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="C39" s="62">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="63" t="s">
-        <v>220</v>
-      </c>
-      <c r="C40" s="63">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="62" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="63" t="s">
-        <v>221</v>
-      </c>
-      <c r="C42" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="62" t="s">
-        <v>222</v>
-      </c>
-      <c r="C43" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="C44" s="63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="62" t="s">
-        <v>224</v>
-      </c>
-      <c r="C45" s="62">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="63" t="s">
-        <v>225</v>
-      </c>
-      <c r="C46" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="62" t="s">
-        <v>226</v>
-      </c>
-      <c r="C47" s="62">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="63" t="s">
-        <v>227</v>
-      </c>
-      <c r="C48" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="62" t="s">
-        <v>228</v>
-      </c>
-      <c r="C49" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="63" t="s">
-        <v>229</v>
-      </c>
-      <c r="C50" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="C51" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="C52" s="63">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="C53" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="63" t="s">
-        <v>232</v>
-      </c>
-      <c r="C54" s="63">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="C55" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="63" t="s">
-        <v>234</v>
-      </c>
-      <c r="C56" s="63">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="C57" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="63" t="s">
-        <v>236</v>
-      </c>
-      <c r="C58" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="62"/>
-      <c r="C59" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="63" t="s">
-        <v>237</v>
-      </c>
-      <c r="C60" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="62" t="s">
-        <v>238</v>
-      </c>
-      <c r="C61" s="62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="63" t="s">
-        <v>239</v>
-      </c>
-      <c r="C62" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="62" t="s">
-        <v>240</v>
-      </c>
-      <c r="C63" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="C64" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="62" t="s">
-        <v>183</v>
-      </c>
-      <c r="C65" s="62">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="63" t="s">
-        <v>184</v>
-      </c>
-      <c r="C66" s="63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="62" t="s">
-        <v>241</v>
-      </c>
-      <c r="C67" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="C68" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="62" t="s">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="57" t="s">
         <v>243</v>
       </c>
-      <c r="C69" s="62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="63" t="s">
+      <c r="C70" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="56" t="s">
         <v>244</v>
       </c>
-      <c r="C70" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="62" t="s">
+      <c r="C71" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="C71" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="63" t="s">
+      <c r="C72" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="C72" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="62" t="s">
+      <c r="C73" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="57" t="s">
         <v>247</v>
       </c>
-      <c r="C73" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="63" t="s">
+      <c r="C74" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C75" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="C74" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="C75" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="63" t="s">
+      <c r="C76" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="56" t="s">
         <v>249</v>
       </c>
-      <c r="C76" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="62" t="s">
+      <c r="C77" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="57" t="s">
         <v>250</v>
       </c>
-      <c r="C77" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="63" t="s">
+      <c r="C78" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C79" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="C78" s="63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="62" t="s">
-        <v>193</v>
-      </c>
-      <c r="C79" s="62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="63" t="s">
-        <v>252</v>
-      </c>
-      <c r="C80" s="63">
+      <c r="C80" s="57">
         <v>1</v>
       </c>
     </row>

--- a/Deliverables/BOM/ARC_1.0.5/eSpark_BOM_ARC_1.0.5.xlsx
+++ b/Deliverables/BOM/ARC_1.0.5/eSpark_BOM_ARC_1.0.5.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="460">
   <si>
     <t>Component list</t>
   </si>
@@ -1178,9 +1178,6 @@
     <t>C163551</t>
   </si>
   <si>
-    <t>C47460</t>
-  </si>
-  <si>
     <t>C60580</t>
   </si>
   <si>
@@ -1265,9 +1262,6 @@
     <t>C144601</t>
   </si>
   <si>
-    <t>C861571</t>
-  </si>
-  <si>
     <t>C100044</t>
   </si>
   <si>
@@ -1280,9 +1274,6 @@
     <t>C318893</t>
   </si>
   <si>
-    <t>C232660</t>
-  </si>
-  <si>
     <t>C2960</t>
   </si>
   <si>
@@ -1391,10 +1382,34 @@
     <t>LULU Quote</t>
   </si>
   <si>
-    <t>Custom Supplier</t>
-  </si>
-  <si>
     <t>C3, C4, C7, C8, C13, C18, C20, C23, C24, C32, C36, C37, C38, C41, C42, C45</t>
+  </si>
+  <si>
+    <t>B140-13-F</t>
+  </si>
+  <si>
+    <t>C15759</t>
+  </si>
+  <si>
+    <t>FRC0603J104 TS</t>
+  </si>
+  <si>
+    <t>C2907088</t>
+  </si>
+  <si>
+    <t>FRC0603J824TS</t>
+  </si>
+  <si>
+    <t>C2930044</t>
+  </si>
+  <si>
+    <t>MC78M05BDTRKG</t>
+  </si>
+  <si>
+    <t>C94612</t>
+  </si>
+  <si>
+    <t>LULU</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1421,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1577,6 +1592,24 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1891,7 +1924,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2081,6 +2114,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2113,28 +2170,31 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2513,15 +2573,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="80"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2532,7 +2592,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="50" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2557,7 +2617,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="51" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2571,7 +2631,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="73"/>
+      <c r="S3" s="81"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2582,7 +2642,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="52" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2596,7 +2656,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="74"/>
+      <c r="S4" s="82"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2621,7 +2681,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="74"/>
+      <c r="S5" s="82"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2642,7 +2702,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="74"/>
+      <c r="S6" s="82"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2663,7 +2723,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="74"/>
+      <c r="S7" s="82"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2684,7 +2744,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="74"/>
+      <c r="S8" s="82"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2784,20 +2844,20 @@
         <v>10</v>
       </c>
       <c r="N10" s="46">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O10" s="58" t="s">
         <v>368</v>
       </c>
       <c r="P10" s="49">
-        <v>0.24690000000000001</v>
+        <v>0.29320000000000002</v>
       </c>
       <c r="Q10" s="49">
         <f>P10*N10</f>
-        <v>2.7159</v>
+        <v>4.3980000000000006</v>
       </c>
       <c r="R10" s="48"/>
-      <c r="S10" s="81"/>
+      <c r="S10" s="71"/>
     </row>
     <row r="11" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -2805,55 +2865,55 @@
         <f t="shared" ref="B11:B84" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="84" t="s">
+      <c r="E11" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="83" t="s">
+      <c r="F11" s="73" t="s">
         <v>354</v>
       </c>
-      <c r="G11" s="83" t="s">
+      <c r="G11" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="H11" s="83" t="s">
+      <c r="H11" s="73" t="s">
         <v>254</v>
       </c>
-      <c r="I11" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J11" s="83" t="s">
+      <c r="I11" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J11" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="K11" s="83" t="s">
+      <c r="K11" s="73" t="s">
         <v>300</v>
       </c>
-      <c r="L11" s="84">
+      <c r="L11" s="74">
         <v>3</v>
       </c>
-      <c r="M11" s="83">
+      <c r="M11" s="73">
         <f t="shared" ref="M11:M71" si="1">L11*5</f>
         <v>15</v>
       </c>
-      <c r="N11" s="83">
+      <c r="N11" s="73">
         <v>16</v>
       </c>
-      <c r="O11" s="85" t="s">
+      <c r="O11" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P11" s="86">
-        <v>0.40799999999999997</v>
-      </c>
-      <c r="Q11" s="86">
+      <c r="P11" s="76">
+        <v>0.37390000000000001</v>
+      </c>
+      <c r="Q11" s="76">
         <f t="shared" ref="Q11:Q71" si="2">P11*N11</f>
-        <v>6.5279999999999996</v>
-      </c>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
+        <v>5.9824000000000002</v>
+      </c>
+      <c r="R11" s="77"/>
+      <c r="S11" s="77"/>
     </row>
     <row r="12" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -2865,7 +2925,7 @@
         <v>341</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E12" s="47" t="s">
         <v>81</v>
@@ -2902,14 +2962,14 @@
         <v>368</v>
       </c>
       <c r="P12" s="49">
-        <v>6.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q12" s="49">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="R12" s="48"/>
-      <c r="S12" s="81"/>
+      <c r="S12" s="71"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -2917,55 +2977,55 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="D13" s="83" t="s">
+      <c r="D13" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="84" t="s">
+      <c r="E13" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="G13" s="83" t="s">
+      <c r="G13" s="73" t="s">
         <v>195</v>
       </c>
-      <c r="H13" s="83" t="s">
+      <c r="H13" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="I13" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J13" s="83" t="s">
+      <c r="I13" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J13" s="73" t="s">
         <v>371</v>
       </c>
-      <c r="K13" s="83" t="s">
+      <c r="K13" s="73" t="s">
         <v>302</v>
       </c>
-      <c r="L13" s="84">
-        <v>1</v>
-      </c>
-      <c r="M13" s="83">
+      <c r="L13" s="74">
+        <v>1</v>
+      </c>
+      <c r="M13" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N13" s="83">
+      <c r="N13" s="73">
         <v>6</v>
       </c>
-      <c r="O13" s="85" t="s">
+      <c r="O13" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P13" s="86">
-        <v>0.8125</v>
-      </c>
-      <c r="Q13" s="86">
+      <c r="P13" s="76">
+        <v>1.4064000000000001</v>
+      </c>
+      <c r="Q13" s="76">
         <f t="shared" si="2"/>
-        <v>4.875</v>
-      </c>
-      <c r="R13" s="87"/>
-      <c r="S13" s="87"/>
+        <v>8.4384000000000015</v>
+      </c>
+      <c r="R13" s="77"/>
+      <c r="S13" s="77"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -3014,14 +3074,14 @@
         <v>368</v>
       </c>
       <c r="P14" s="49">
-        <v>3.5299999999999998E-2</v>
+        <v>3.6600000000000001E-2</v>
       </c>
       <c r="Q14" s="49">
         <f t="shared" si="2"/>
-        <v>1.0589999999999999</v>
+        <v>1.0980000000000001</v>
       </c>
       <c r="R14" s="48"/>
-      <c r="S14" s="81"/>
+      <c r="S14" s="71"/>
     </row>
     <row r="15" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
@@ -3029,55 +3089,55 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="82" t="s">
+      <c r="C15" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="84" t="s">
+      <c r="E15" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="F15" s="83" t="s">
+      <c r="F15" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="G15" s="83" t="s">
+      <c r="G15" s="73" t="s">
         <v>196</v>
       </c>
-      <c r="H15" s="83" t="s">
+      <c r="H15" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I15" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J15" s="83" t="s">
+      <c r="I15" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J15" s="73" t="s">
         <v>374</v>
       </c>
-      <c r="K15" s="83" t="s">
+      <c r="K15" s="73" t="s">
         <v>304</v>
       </c>
-      <c r="L15" s="84">
+      <c r="L15" s="74">
         <v>2</v>
       </c>
-      <c r="M15" s="83">
+      <c r="M15" s="73">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N15" s="83">
+      <c r="N15" s="73">
         <v>100</v>
       </c>
-      <c r="O15" s="85" t="s">
+      <c r="O15" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P15" s="86">
-        <v>2.8E-3</v>
-      </c>
-      <c r="Q15" s="86">
+      <c r="P15" s="76">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q15" s="76">
         <f t="shared" si="2"/>
-        <v>0.27999999999999997</v>
-      </c>
-      <c r="R15" s="87"/>
-      <c r="S15" s="87"/>
+        <v>0.27</v>
+      </c>
+      <c r="R15" s="77"/>
+      <c r="S15" s="77"/>
     </row>
     <row r="16" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -3126,14 +3186,14 @@
         <v>368</v>
       </c>
       <c r="P16" s="49">
-        <v>4.1999999999999997E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q16" s="49">
         <f t="shared" si="2"/>
-        <v>0.42</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="R16" s="48"/>
-      <c r="S16" s="81"/>
+      <c r="S16" s="71"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
@@ -3141,55 +3201,55 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="D17" s="83" t="s">
+      <c r="D17" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="84" t="s">
+      <c r="E17" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="H17" s="73" t="s">
         <v>259</v>
       </c>
-      <c r="I17" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J17" s="83" t="s">
+      <c r="I17" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J17" s="73" t="s">
         <v>376</v>
       </c>
-      <c r="K17" s="83" t="s">
+      <c r="K17" s="73" t="s">
         <v>303</v>
       </c>
-      <c r="L17" s="84">
+      <c r="L17" s="74">
         <v>2</v>
       </c>
-      <c r="M17" s="83">
+      <c r="M17" s="73">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N17" s="83">
+      <c r="N17" s="73">
         <v>20</v>
       </c>
-      <c r="O17" s="85" t="s">
+      <c r="O17" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P17" s="86">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="Q17" s="86">
+      <c r="P17" s="76">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="Q17" s="76">
         <f t="shared" si="2"/>
-        <v>0.28400000000000003</v>
-      </c>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="R17" s="77"/>
+      <c r="S17" s="77"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -3238,14 +3298,14 @@
         <v>368</v>
       </c>
       <c r="P18" s="49">
-        <v>5.1000000000000004E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="Q18" s="49">
         <f t="shared" si="2"/>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="R18" s="48"/>
-      <c r="S18" s="81"/>
+      <c r="S18" s="71"/>
     </row>
     <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -3253,55 +3313,55 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="D19" s="83" t="s">
+      <c r="D19" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="84" t="s">
+      <c r="E19" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="83" t="s">
+      <c r="F19" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="G19" s="83" t="s">
+      <c r="G19" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="H19" s="83" t="s">
+      <c r="H19" s="73" t="s">
         <v>260</v>
       </c>
-      <c r="I19" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J19" s="83" t="s">
+      <c r="I19" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J19" s="73" t="s">
         <v>378</v>
       </c>
-      <c r="K19" s="83" t="s">
+      <c r="K19" s="73" t="s">
         <v>307</v>
       </c>
-      <c r="L19" s="84">
+      <c r="L19" s="74">
         <v>2</v>
       </c>
-      <c r="M19" s="83">
+      <c r="M19" s="73">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N19" s="83">
+      <c r="N19" s="73">
         <v>20</v>
       </c>
-      <c r="O19" s="85" t="s">
+      <c r="O19" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P19" s="86">
-        <v>3.2899999999999999E-2</v>
-      </c>
-      <c r="Q19" s="86">
+      <c r="P19" s="76">
+        <v>2.98E-2</v>
+      </c>
+      <c r="Q19" s="76">
         <f t="shared" si="2"/>
-        <v>0.65799999999999992</v>
-      </c>
-      <c r="R19" s="87"/>
-      <c r="S19" s="87"/>
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="R19" s="77"/>
+      <c r="S19" s="77"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -3350,14 +3410,14 @@
         <v>368</v>
       </c>
       <c r="P20" s="49">
-        <v>2.8999999999999998E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q20" s="49">
         <f t="shared" si="2"/>
-        <v>0.28999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="R20" s="48"/>
-      <c r="S20" s="81"/>
+      <c r="S20" s="71"/>
     </row>
     <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -3365,55 +3425,55 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="82" t="s">
+      <c r="C21" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="D21" s="83" t="s">
+      <c r="D21" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="84" t="s">
+      <c r="E21" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="83" t="s">
+      <c r="F21" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="83" t="s">
+      <c r="G21" s="73" t="s">
         <v>202</v>
       </c>
-      <c r="H21" s="83" t="s">
+      <c r="H21" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I21" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J21" s="83" t="s">
+      <c r="I21" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J21" s="73" t="s">
         <v>380</v>
       </c>
-      <c r="K21" s="83" t="s">
+      <c r="K21" s="73" t="s">
         <v>309</v>
       </c>
-      <c r="L21" s="84">
-        <v>1</v>
-      </c>
-      <c r="M21" s="83">
+      <c r="L21" s="74">
+        <v>1</v>
+      </c>
+      <c r="M21" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N21" s="83">
+      <c r="N21" s="73">
         <v>100</v>
       </c>
-      <c r="O21" s="85" t="s">
+      <c r="O21" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P21" s="86">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="Q21" s="86">
+      <c r="P21" s="76">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="Q21" s="76">
         <f t="shared" si="2"/>
-        <v>0.37</v>
-      </c>
-      <c r="R21" s="87"/>
-      <c r="S21" s="87"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R21" s="77"/>
+      <c r="S21" s="77"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -3425,7 +3485,7 @@
         <v>341</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E22" s="47" t="s">
         <v>91</v>
@@ -3440,10 +3500,10 @@
         <v>260</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="K22" s="46" t="s">
         <v>310</v>
@@ -3462,14 +3522,14 @@
         <v>368</v>
       </c>
       <c r="P22" s="49">
-        <v>3.2099999999999997E-2</v>
+        <v>2.8299999999999999E-2</v>
       </c>
       <c r="Q22" s="49">
         <f t="shared" si="2"/>
-        <v>0.6419999999999999</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="R22" s="48"/>
-      <c r="S22" s="81"/>
+      <c r="S22" s="71"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -3477,55 +3537,55 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="82" t="s">
+      <c r="C23" s="72" t="s">
         <v>341</v>
       </c>
-      <c r="D23" s="83" t="s">
+      <c r="D23" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="84" t="s">
+      <c r="E23" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="83" t="s">
+      <c r="F23" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="G23" s="83" t="s">
+      <c r="G23" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="H23" s="83" t="s">
+      <c r="H23" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I23" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J23" s="83" t="s">
+      <c r="I23" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J23" s="73" t="s">
         <v>381</v>
       </c>
-      <c r="K23" s="83" t="s">
+      <c r="K23" s="73" t="s">
         <v>311</v>
       </c>
-      <c r="L23" s="84">
-        <v>1</v>
-      </c>
-      <c r="M23" s="83">
+      <c r="L23" s="74">
+        <v>1</v>
+      </c>
+      <c r="M23" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N23" s="83">
+      <c r="N23" s="73">
         <v>100</v>
       </c>
-      <c r="O23" s="85" t="s">
+      <c r="O23" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P23" s="86">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="Q23" s="86">
+      <c r="P23" s="76">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q23" s="76">
         <f t="shared" si="2"/>
-        <v>0.38999999999999996</v>
-      </c>
-      <c r="R23" s="87"/>
-      <c r="S23" s="87"/>
+        <v>0.38</v>
+      </c>
+      <c r="R23" s="77"/>
+      <c r="S23" s="77"/>
     </row>
     <row r="24" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -3555,7 +3615,7 @@
         <v>355</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K24" s="46" t="s">
         <v>355</v>
@@ -3574,14 +3634,14 @@
         <v>368</v>
       </c>
       <c r="P24" s="49">
-        <v>9.9699999999999997E-2</v>
+        <v>9.1399999999999995E-2</v>
       </c>
       <c r="Q24" s="49">
         <f t="shared" si="2"/>
-        <v>0.997</v>
+        <v>0.91399999999999992</v>
       </c>
       <c r="R24" s="48"/>
-      <c r="S24" s="81"/>
+      <c r="S24" s="71"/>
     </row>
     <row r="25" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -3589,55 +3649,55 @@
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="82" t="s">
+      <c r="C25" s="72" t="s">
         <v>342</v>
       </c>
-      <c r="D25" s="83" t="s">
+      <c r="D25" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="84" t="s">
+      <c r="E25" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="83" t="s">
+      <c r="F25" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="83" t="s">
+      <c r="G25" s="78" t="s">
         <v>207</v>
       </c>
-      <c r="H25" s="83" t="s">
+      <c r="H25" s="73" t="s">
         <v>263</v>
       </c>
-      <c r="I25" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J25" s="83" t="s">
-        <v>382</v>
-      </c>
-      <c r="K25" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L25" s="84">
+      <c r="I25" s="73" t="s">
+        <v>451</v>
+      </c>
+      <c r="J25" s="73" t="s">
+        <v>452</v>
+      </c>
+      <c r="K25" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L25" s="74">
         <v>3</v>
       </c>
-      <c r="M25" s="83">
+      <c r="M25" s="73">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N25" s="83">
+      <c r="N25" s="73">
         <v>20</v>
       </c>
-      <c r="O25" s="85" t="s">
+      <c r="O25" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P25" s="86">
-        <v>6.4199999999999993E-2</v>
-      </c>
-      <c r="Q25" s="86">
+      <c r="P25" s="76">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="Q25" s="76">
         <f t="shared" si="2"/>
-        <v>1.2839999999999998</v>
-      </c>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="R25" s="77"/>
+      <c r="S25" s="77"/>
     </row>
     <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -3667,7 +3727,7 @@
         <v>355</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="K26" s="46" t="s">
         <v>355</v>
@@ -3686,14 +3746,14 @@
         <v>368</v>
       </c>
       <c r="P26" s="49">
-        <v>3.8899999999999997E-2</v>
+        <v>3.85E-2</v>
       </c>
       <c r="Q26" s="49">
         <f t="shared" si="2"/>
-        <v>0.77799999999999991</v>
+        <v>0.77</v>
       </c>
       <c r="R26" s="48"/>
-      <c r="S26" s="81"/>
+      <c r="S26" s="71"/>
     </row>
     <row r="27" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -3701,55 +3761,55 @@
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="82" t="s">
+      <c r="C27" s="72" t="s">
         <v>342</v>
       </c>
-      <c r="D27" s="83" t="s">
+      <c r="D27" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="84" t="s">
+      <c r="E27" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="83" t="s">
+      <c r="F27" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="G27" s="83" t="s">
+      <c r="G27" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="H27" s="83" t="s">
+      <c r="H27" s="73" t="s">
         <v>262</v>
       </c>
-      <c r="I27" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J27" s="83" t="s">
-        <v>430</v>
-      </c>
-      <c r="K27" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L27" s="84">
+      <c r="I27" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J27" s="73" t="s">
+        <v>427</v>
+      </c>
+      <c r="K27" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L27" s="74">
         <v>4</v>
       </c>
-      <c r="M27" s="83">
+      <c r="M27" s="73">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="83">
+      <c r="N27" s="73">
         <v>50</v>
       </c>
-      <c r="O27" s="85" t="s">
+      <c r="O27" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P27" s="86">
-        <v>9.7000000000000003E-3</v>
-      </c>
-      <c r="Q27" s="86">
+      <c r="P27" s="76">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="Q27" s="76">
         <f t="shared" si="2"/>
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="R27" s="87"/>
-      <c r="S27" s="87"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="R27" s="77"/>
+      <c r="S27" s="77"/>
     </row>
     <row r="28" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -3779,7 +3839,7 @@
         <v>355</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K28" s="46" t="s">
         <v>355</v>
@@ -3798,14 +3858,14 @@
         <v>368</v>
       </c>
       <c r="P28" s="49">
-        <v>5.6399999999999999E-2</v>
+        <v>5.6599999999999998E-2</v>
       </c>
       <c r="Q28" s="49">
         <f t="shared" si="2"/>
-        <v>0.56399999999999995</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="R28" s="48"/>
-      <c r="S28" s="81"/>
+      <c r="S28" s="71"/>
     </row>
     <row r="29" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -3813,55 +3873,55 @@
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="82" t="s">
+      <c r="C29" s="72" t="s">
         <v>342</v>
       </c>
-      <c r="D29" s="83" t="s">
+      <c r="D29" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="84" t="s">
+      <c r="E29" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="83" t="s">
+      <c r="F29" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="G29" s="83" t="s">
+      <c r="G29" s="73" t="s">
         <v>210</v>
       </c>
-      <c r="H29" s="83" t="s">
+      <c r="H29" s="73" t="s">
         <v>266</v>
       </c>
-      <c r="I29" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J29" s="83" t="s">
-        <v>432</v>
-      </c>
-      <c r="K29" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L29" s="84">
-        <v>1</v>
-      </c>
-      <c r="M29" s="83">
+      <c r="I29" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J29" s="73" t="s">
+        <v>429</v>
+      </c>
+      <c r="K29" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L29" s="74">
+        <v>1</v>
+      </c>
+      <c r="M29" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N29" s="83">
+      <c r="N29" s="73">
         <v>10</v>
       </c>
-      <c r="O29" s="85" t="s">
+      <c r="O29" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P29" s="86">
-        <v>6.5100000000000005E-2</v>
-      </c>
-      <c r="Q29" s="86">
+      <c r="P29" s="76">
+        <v>5.9299999999999999E-2</v>
+      </c>
+      <c r="Q29" s="76">
         <f t="shared" si="2"/>
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="R29" s="87"/>
-      <c r="S29" s="87"/>
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="R29" s="77"/>
+      <c r="S29" s="77"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -3891,7 +3951,7 @@
         <v>355</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K30" s="46" t="s">
         <v>355</v>
@@ -3910,14 +3970,14 @@
         <v>368</v>
       </c>
       <c r="P30" s="49">
-        <v>2.5499999999999998E-2</v>
+        <v>0.1163</v>
       </c>
       <c r="Q30" s="49">
         <f t="shared" si="2"/>
-        <v>0.51</v>
+        <v>2.3260000000000001</v>
       </c>
       <c r="R30" s="48"/>
-      <c r="S30" s="81"/>
+      <c r="S30" s="71"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3925,55 +3985,55 @@
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="72" t="s">
         <v>343</v>
       </c>
-      <c r="D31" s="83" t="s">
+      <c r="D31" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="84" t="s">
+      <c r="E31" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="83" t="s">
+      <c r="F31" s="73" t="s">
         <v>354</v>
       </c>
-      <c r="G31" s="88" t="s">
+      <c r="G31" s="78" t="s">
         <v>163</v>
       </c>
-      <c r="H31" s="83" t="s">
+      <c r="H31" s="73" t="s">
         <v>268</v>
       </c>
-      <c r="I31" s="83" t="s">
-        <v>433</v>
-      </c>
-      <c r="J31" s="83" t="s">
-        <v>434</v>
-      </c>
-      <c r="K31" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L31" s="84">
-        <v>1</v>
-      </c>
-      <c r="M31" s="83">
+      <c r="I31" s="73" t="s">
+        <v>430</v>
+      </c>
+      <c r="J31" s="73" t="s">
+        <v>431</v>
+      </c>
+      <c r="K31" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L31" s="74">
+        <v>1</v>
+      </c>
+      <c r="M31" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N31" s="83">
+      <c r="N31" s="73">
         <v>10</v>
       </c>
-      <c r="O31" s="85" t="s">
+      <c r="O31" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P31" s="86">
-        <v>0.1207</v>
-      </c>
-      <c r="Q31" s="86">
+      <c r="P31" s="76">
+        <v>0.1163</v>
+      </c>
+      <c r="Q31" s="76">
         <f t="shared" si="2"/>
-        <v>1.2070000000000001</v>
-      </c>
-      <c r="R31" s="87"/>
-      <c r="S31" s="87"/>
+        <v>1.163</v>
+      </c>
+      <c r="R31" s="77"/>
+      <c r="S31" s="77"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -4000,10 +4060,10 @@
         <v>268</v>
       </c>
       <c r="I32" s="46" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J32" s="46" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K32" s="46" t="s">
         <v>355</v>
@@ -4022,14 +4082,14 @@
         <v>368</v>
       </c>
       <c r="P32" s="49">
-        <v>7.0300000000000001E-2</v>
+        <v>7.1199999999999999E-2</v>
       </c>
       <c r="Q32" s="49">
         <f t="shared" si="2"/>
-        <v>0.70300000000000007</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="R32" s="48"/>
-      <c r="S32" s="81"/>
+      <c r="S32" s="71"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -4037,55 +4097,55 @@
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="82" t="s">
+      <c r="C33" s="72" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="83" t="s">
+      <c r="D33" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="84" t="s">
+      <c r="E33" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="F33" s="83" t="s">
+      <c r="F33" s="73" t="s">
         <v>354</v>
       </c>
-      <c r="G33" s="83" t="s">
+      <c r="G33" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="H33" s="83" t="s">
+      <c r="H33" s="73" t="s">
         <v>269</v>
       </c>
-      <c r="I33" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J33" s="83" t="s">
-        <v>384</v>
-      </c>
-      <c r="K33" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L33" s="84">
-        <v>1</v>
-      </c>
-      <c r="M33" s="83">
+      <c r="I33" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J33" s="73" t="s">
+        <v>383</v>
+      </c>
+      <c r="K33" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L33" s="74">
+        <v>1</v>
+      </c>
+      <c r="M33" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N33" s="83">
+      <c r="N33" s="73">
         <v>10</v>
       </c>
-      <c r="O33" s="85" t="s">
+      <c r="O33" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P33" s="86">
-        <v>8.8400000000000006E-2</v>
-      </c>
-      <c r="Q33" s="86">
+      <c r="P33" s="76">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="Q33" s="76">
         <f t="shared" si="2"/>
-        <v>0.88400000000000012</v>
-      </c>
-      <c r="R33" s="87"/>
-      <c r="S33" s="87"/>
+        <v>0.80799999999999994</v>
+      </c>
+      <c r="R33" s="77"/>
+      <c r="S33" s="77"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -4115,7 +4175,7 @@
         <v>355</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K34" s="46" t="s">
         <v>355</v>
@@ -4141,7 +4201,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="R34" s="48"/>
-      <c r="S34" s="81"/>
+      <c r="S34" s="71"/>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -4149,55 +4209,55 @@
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="82" t="s">
+      <c r="C35" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="D35" s="83" t="s">
+      <c r="D35" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="84" t="s">
+      <c r="E35" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="F35" s="83" t="s">
+      <c r="F35" s="73" t="s">
         <v>354</v>
       </c>
-      <c r="G35" s="83" t="s">
+      <c r="G35" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="H35" s="83" t="s">
+      <c r="H35" s="73" t="s">
         <v>264</v>
       </c>
-      <c r="I35" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J35" s="83" t="s">
-        <v>386</v>
-      </c>
-      <c r="K35" s="83" t="s">
+      <c r="I35" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J35" s="73" t="s">
+        <v>385</v>
+      </c>
+      <c r="K35" s="73" t="s">
         <v>312</v>
       </c>
-      <c r="L35" s="84">
-        <v>1</v>
-      </c>
-      <c r="M35" s="83">
+      <c r="L35" s="74">
+        <v>1</v>
+      </c>
+      <c r="M35" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N35" s="83">
+      <c r="N35" s="73">
         <v>6</v>
       </c>
-      <c r="O35" s="85" t="s">
+      <c r="O35" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P35" s="86">
-        <v>0.754</v>
-      </c>
-      <c r="Q35" s="86">
+      <c r="P35" s="76">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="Q35" s="76">
         <f t="shared" si="2"/>
-        <v>4.524</v>
-      </c>
-      <c r="R35" s="87"/>
-      <c r="S35" s="87"/>
+        <v>4.2959999999999994</v>
+      </c>
+      <c r="R35" s="77"/>
+      <c r="S35" s="77"/>
     </row>
     <row r="36" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -4227,7 +4287,7 @@
         <v>355</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K36" s="46" t="s">
         <v>313</v>
@@ -4246,14 +4306,14 @@
         <v>368</v>
       </c>
       <c r="P36" s="49">
-        <v>8.3299999999999999E-2</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="Q36" s="49">
         <f t="shared" si="2"/>
-        <v>0.83299999999999996</v>
+        <v>0.79699999999999993</v>
       </c>
       <c r="R36" s="48"/>
-      <c r="S36" s="81"/>
+      <c r="S36" s="71"/>
     </row>
     <row r="37" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
@@ -4261,55 +4321,55 @@
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="82" t="s">
+      <c r="C37" s="72" t="s">
         <v>346</v>
       </c>
-      <c r="D37" s="83" t="s">
+      <c r="D37" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="84" t="s">
+      <c r="E37" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="F37" s="83" t="s">
+      <c r="F37" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="G37" s="83" t="s">
+      <c r="G37" s="73" t="s">
         <v>214</v>
       </c>
-      <c r="H37" s="83" t="s">
+      <c r="H37" s="73" t="s">
         <v>271</v>
       </c>
-      <c r="I37" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J37" s="83" t="s">
-        <v>388</v>
-      </c>
-      <c r="K37" s="83" t="s">
+      <c r="I37" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J37" s="73" t="s">
+        <v>387</v>
+      </c>
+      <c r="K37" s="73" t="s">
         <v>314</v>
       </c>
-      <c r="L37" s="84">
-        <v>1</v>
-      </c>
-      <c r="M37" s="83">
+      <c r="L37" s="74">
+        <v>1</v>
+      </c>
+      <c r="M37" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N37" s="83">
+      <c r="N37" s="73">
         <v>10</v>
       </c>
-      <c r="O37" s="85" t="s">
+      <c r="O37" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P37" s="86">
-        <v>2.7300000000000001E-2</v>
-      </c>
-      <c r="Q37" s="86">
+      <c r="P37" s="76">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="Q37" s="76">
         <f t="shared" si="2"/>
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="R37" s="87"/>
-      <c r="S37" s="87"/>
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
     </row>
     <row r="38" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -4336,10 +4396,10 @@
         <v>272</v>
       </c>
       <c r="I38" s="46" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J38" s="46" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="K38" s="46" t="s">
         <v>315</v>
@@ -4358,14 +4418,14 @@
         <v>368</v>
       </c>
       <c r="P38" s="49">
-        <v>1.5900000000000001E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="Q38" s="49">
         <f t="shared" si="2"/>
-        <v>0.79500000000000004</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="R38" s="48"/>
-      <c r="S38" s="81"/>
+      <c r="S38" s="71"/>
     </row>
     <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
@@ -4373,55 +4433,55 @@
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="82" t="s">
+      <c r="C39" s="72" t="s">
         <v>347</v>
       </c>
-      <c r="D39" s="83" t="s">
+      <c r="D39" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="84" t="s">
+      <c r="E39" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="F39" s="83" t="s">
+      <c r="F39" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="G39" s="88" t="s">
+      <c r="G39" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="H39" s="83" t="s">
+      <c r="H39" s="73" t="s">
         <v>272</v>
       </c>
-      <c r="I39" s="83" t="s">
-        <v>437</v>
-      </c>
-      <c r="J39" s="83" t="s">
-        <v>438</v>
-      </c>
-      <c r="K39" s="83" t="s">
+      <c r="I39" s="73" t="s">
+        <v>434</v>
+      </c>
+      <c r="J39" s="73" t="s">
+        <v>435</v>
+      </c>
+      <c r="K39" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="L39" s="84">
-        <v>1</v>
-      </c>
-      <c r="M39" s="83">
+      <c r="L39" s="74">
+        <v>1</v>
+      </c>
+      <c r="M39" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N39" s="83">
+      <c r="N39" s="73">
         <v>10</v>
       </c>
-      <c r="O39" s="85" t="s">
+      <c r="O39" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P39" s="86">
-        <v>3.9199999999999999E-2</v>
-      </c>
-      <c r="Q39" s="86">
+      <c r="P39" s="76">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="Q39" s="76">
         <f t="shared" si="2"/>
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="R39" s="87"/>
-      <c r="S39" s="87"/>
+        <v>0.40099999999999997</v>
+      </c>
+      <c r="R39" s="77"/>
+      <c r="S39" s="77"/>
     </row>
     <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
@@ -4451,7 +4511,7 @@
         <v>355</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K40" s="46" t="s">
         <v>355</v>
@@ -4464,20 +4524,20 @@
         <v>5</v>
       </c>
       <c r="N40" s="46">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O40" s="58" t="s">
         <v>368</v>
       </c>
       <c r="P40" s="49">
-        <v>0.48880000000000001</v>
+        <v>0.3352</v>
       </c>
       <c r="Q40" s="49">
         <f t="shared" si="2"/>
-        <v>2.9328000000000003</v>
+        <v>3.3519999999999999</v>
       </c>
       <c r="R40" s="48"/>
-      <c r="S40" s="81"/>
+      <c r="S40" s="71"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -4485,55 +4545,55 @@
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="82" t="s">
+      <c r="C41" s="72" t="s">
         <v>349</v>
       </c>
-      <c r="D41" s="83" t="s">
+      <c r="D41" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="E41" s="84" t="s">
+      <c r="E41" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="F41" s="83" t="s">
+      <c r="F41" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="G41" s="88" t="s">
+      <c r="G41" s="78" t="s">
         <v>217</v>
       </c>
-      <c r="H41" s="83" t="s">
+      <c r="H41" s="73" t="s">
         <v>274</v>
       </c>
-      <c r="I41" s="83" t="s">
-        <v>441</v>
-      </c>
-      <c r="J41" s="83" t="s">
-        <v>442</v>
-      </c>
-      <c r="K41" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L41" s="84">
-        <v>1</v>
-      </c>
-      <c r="M41" s="83">
+      <c r="I41" s="73" t="s">
+        <v>438</v>
+      </c>
+      <c r="J41" s="73" t="s">
+        <v>439</v>
+      </c>
+      <c r="K41" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L41" s="74">
+        <v>1</v>
+      </c>
+      <c r="M41" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N41" s="83">
+      <c r="N41" s="73">
         <v>20</v>
       </c>
-      <c r="O41" s="85" t="s">
+      <c r="O41" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P41" s="86">
-        <v>3.2599999999999997E-2</v>
-      </c>
-      <c r="Q41" s="86">
+      <c r="P41" s="76">
+        <v>3.0700000000000002E-2</v>
+      </c>
+      <c r="Q41" s="76">
         <f t="shared" si="2"/>
-        <v>0.65199999999999991</v>
-      </c>
-      <c r="R41" s="87"/>
-      <c r="S41" s="87"/>
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="R41" s="77"/>
+      <c r="S41" s="77"/>
     </row>
     <row r="42" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -4563,7 +4623,7 @@
         <v>355</v>
       </c>
       <c r="J42" s="46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K42" s="46" t="s">
         <v>355</v>
@@ -4582,14 +4642,14 @@
         <v>368</v>
       </c>
       <c r="P42" s="49">
-        <v>5.8099999999999999E-2</v>
+        <v>5.57E-2</v>
       </c>
       <c r="Q42" s="49">
         <f t="shared" si="2"/>
-        <v>0.58099999999999996</v>
+        <v>0.55699999999999994</v>
       </c>
       <c r="R42" s="48"/>
-      <c r="S42" s="81"/>
+      <c r="S42" s="71"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -4597,55 +4657,55 @@
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="82" t="s">
+      <c r="C43" s="72" t="s">
         <v>349</v>
       </c>
-      <c r="D43" s="83" t="s">
+      <c r="D43" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="E43" s="84" t="s">
+      <c r="E43" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="F43" s="83" t="s">
+      <c r="F43" s="73" t="s">
         <v>173</v>
       </c>
-      <c r="G43" s="88">
+      <c r="G43" s="78">
         <v>61300611121</v>
       </c>
-      <c r="H43" s="83" t="s">
+      <c r="H43" s="73" t="s">
         <v>276</v>
       </c>
-      <c r="I43" s="83" t="s">
-        <v>443</v>
-      </c>
-      <c r="J43" s="83" t="s">
-        <v>444</v>
-      </c>
-      <c r="K43" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L43" s="84">
-        <v>1</v>
-      </c>
-      <c r="M43" s="83">
+      <c r="I43" s="73" t="s">
+        <v>440</v>
+      </c>
+      <c r="J43" s="73" t="s">
+        <v>441</v>
+      </c>
+      <c r="K43" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L43" s="74">
+        <v>1</v>
+      </c>
+      <c r="M43" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N43" s="83">
+      <c r="N43" s="73">
         <v>20</v>
       </c>
-      <c r="O43" s="85" t="s">
+      <c r="O43" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P43" s="86">
-        <v>3.5499999999999997E-2</v>
-      </c>
-      <c r="Q43" s="86">
+      <c r="P43" s="76">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="Q43" s="76">
         <f t="shared" si="2"/>
-        <v>0.71</v>
-      </c>
-      <c r="R43" s="87"/>
-      <c r="S43" s="87"/>
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="R43" s="77"/>
+      <c r="S43" s="77"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -4653,43 +4713,54 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="54" t="s">
+      <c r="C44" s="89" t="s">
         <v>317</v>
       </c>
-      <c r="D44" s="46" t="s">
+      <c r="D44" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="E44" s="47" t="s">
+      <c r="E44" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="F44" s="46" t="s">
+      <c r="F44" s="90" t="s">
         <v>174</v>
       </c>
-      <c r="G44" s="47" t="s">
-        <v>355</v>
-      </c>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46" t="s">
-        <v>355</v>
-      </c>
-      <c r="L44" s="47">
+      <c r="G44" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="H44" s="90" t="s">
+        <v>355</v>
+      </c>
+      <c r="I44" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="J44" s="90" t="s">
+        <v>355</v>
+      </c>
+      <c r="K44" s="90" t="s">
+        <v>355</v>
+      </c>
+      <c r="L44" s="59">
         <v>2</v>
       </c>
-      <c r="M44" s="46">
+      <c r="M44" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N44" s="46"/>
-      <c r="O44" s="58"/>
-      <c r="P44" s="49"/>
-      <c r="Q44" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R44" s="48"/>
-      <c r="S44" s="81"/>
+      <c r="N44" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="O44" s="90" t="s">
+        <v>355</v>
+      </c>
+      <c r="P44" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q44" s="90" t="s">
+        <v>355</v>
+      </c>
+      <c r="R44" s="91"/>
+      <c r="S44" s="92"/>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
@@ -4697,55 +4768,55 @@
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="82" t="s">
+      <c r="C45" s="72" t="s">
         <v>350</v>
       </c>
-      <c r="D45" s="83" t="s">
+      <c r="D45" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="84" t="s">
+      <c r="E45" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="F45" s="83" t="s">
+      <c r="F45" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="G45" s="83" t="s">
+      <c r="G45" s="73" t="s">
         <v>218</v>
       </c>
-      <c r="H45" s="83" t="s">
+      <c r="H45" s="73" t="s">
         <v>277</v>
       </c>
-      <c r="I45" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J45" s="83" t="s">
-        <v>391</v>
-      </c>
-      <c r="K45" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L45" s="84">
+      <c r="I45" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J45" s="73" t="s">
+        <v>390</v>
+      </c>
+      <c r="K45" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L45" s="74">
         <v>6</v>
       </c>
-      <c r="M45" s="83">
+      <c r="M45" s="73">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N45" s="83">
+      <c r="N45" s="73">
         <v>40</v>
       </c>
-      <c r="O45" s="85" t="s">
+      <c r="O45" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P45" s="86">
-        <v>2.9600000000000001E-2</v>
-      </c>
-      <c r="Q45" s="86">
+      <c r="P45" s="76">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="Q45" s="76">
         <f t="shared" si="2"/>
-        <v>1.1840000000000002</v>
-      </c>
-      <c r="R45" s="87"/>
-      <c r="S45" s="87"/>
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="R45" s="77"/>
+      <c r="S45" s="77"/>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
@@ -4775,7 +4846,7 @@
         <v>355</v>
       </c>
       <c r="J46" s="46" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K46" s="46" t="s">
         <v>355</v>
@@ -4788,20 +4859,20 @@
         <v>20</v>
       </c>
       <c r="N46" s="46">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O46" s="58" t="s">
         <v>368</v>
       </c>
       <c r="P46" s="49">
-        <v>1.4046000000000001</v>
+        <v>0.80189999999999995</v>
       </c>
       <c r="Q46" s="49">
         <f t="shared" si="2"/>
-        <v>30.901200000000003</v>
+        <v>16.8399</v>
       </c>
       <c r="R46" s="48"/>
-      <c r="S46" s="81"/>
+      <c r="S46" s="71"/>
     </row>
     <row r="47" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
@@ -4809,55 +4880,55 @@
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="82" t="s">
+      <c r="C47" s="72" t="s">
         <v>350</v>
       </c>
-      <c r="D47" s="83" t="s">
+      <c r="D47" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="84" t="s">
+      <c r="E47" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="F47" s="83" t="s">
+      <c r="F47" s="73" t="s">
         <v>356</v>
       </c>
-      <c r="G47" s="83" t="s">
+      <c r="G47" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="H47" s="83" t="s">
+      <c r="H47" s="73" t="s">
         <v>279</v>
       </c>
-      <c r="I47" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J47" s="83" t="s">
-        <v>393</v>
-      </c>
-      <c r="K47" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L47" s="84">
-        <v>1</v>
-      </c>
-      <c r="M47" s="83">
+      <c r="I47" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J47" s="73" t="s">
+        <v>392</v>
+      </c>
+      <c r="K47" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L47" s="74">
+        <v>1</v>
+      </c>
+      <c r="M47" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N47" s="83">
-        <v>6</v>
-      </c>
-      <c r="O47" s="85" t="s">
+      <c r="N47" s="73">
+        <v>10</v>
+      </c>
+      <c r="O47" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P47" s="86">
-        <v>0.4355</v>
-      </c>
-      <c r="Q47" s="86">
+      <c r="P47" s="76">
+        <v>0.32490000000000002</v>
+      </c>
+      <c r="Q47" s="76">
         <f t="shared" si="2"/>
-        <v>2.613</v>
-      </c>
-      <c r="R47" s="87"/>
-      <c r="S47" s="87"/>
+        <v>3.2490000000000001</v>
+      </c>
+      <c r="R47" s="77"/>
+      <c r="S47" s="77"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
@@ -4887,7 +4958,7 @@
         <v>355</v>
       </c>
       <c r="J48" s="46" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K48" s="46" t="s">
         <v>318</v>
@@ -4906,14 +4977,14 @@
         <v>368</v>
       </c>
       <c r="P48" s="49">
-        <v>1.4E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q48" s="49">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="R48" s="48"/>
-      <c r="S48" s="81"/>
+      <c r="S48" s="71"/>
     </row>
     <row r="49" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
@@ -4921,55 +4992,55 @@
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="82" t="s">
+      <c r="C49" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D49" s="83" t="s">
+      <c r="D49" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="84" t="s">
+      <c r="E49" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="F49" s="83" t="s">
+      <c r="F49" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="G49" s="83" t="s">
+      <c r="G49" s="73" t="s">
         <v>221</v>
       </c>
-      <c r="H49" s="83" t="s">
+      <c r="H49" s="73" t="s">
         <v>280</v>
       </c>
-      <c r="I49" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J49" s="83" t="s">
-        <v>395</v>
-      </c>
-      <c r="K49" s="83" t="s">
+      <c r="I49" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J49" s="73" t="s">
+        <v>394</v>
+      </c>
+      <c r="K49" s="73" t="s">
         <v>319</v>
       </c>
-      <c r="L49" s="84">
-        <v>1</v>
-      </c>
-      <c r="M49" s="83">
+      <c r="L49" s="74">
+        <v>1</v>
+      </c>
+      <c r="M49" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N49" s="83">
+      <c r="N49" s="73">
         <v>20</v>
       </c>
-      <c r="O49" s="85" t="s">
+      <c r="O49" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P49" s="86">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="Q49" s="86">
+      <c r="P49" s="76">
+        <v>2.76E-2</v>
+      </c>
+      <c r="Q49" s="76">
         <f t="shared" si="2"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="R49" s="87"/>
-      <c r="S49" s="87"/>
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="R49" s="77"/>
+      <c r="S49" s="77"/>
     </row>
     <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
@@ -4999,7 +5070,7 @@
         <v>355</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K50" s="46" t="s">
         <v>320</v>
@@ -5025,7 +5096,7 @@
         <v>0.61199999999999999</v>
       </c>
       <c r="R50" s="48"/>
-      <c r="S50" s="81"/>
+      <c r="S50" s="71"/>
     </row>
     <row r="51" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -5033,55 +5104,55 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="82" t="s">
+      <c r="C51" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D51" s="83" t="s">
-        <v>446</v>
-      </c>
-      <c r="E51" s="84" t="s">
+      <c r="D51" s="73" t="s">
+        <v>443</v>
+      </c>
+      <c r="E51" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="F51" s="83" t="s">
+      <c r="F51" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="G51" s="83" t="s">
+      <c r="G51" s="73" t="s">
         <v>224</v>
       </c>
-      <c r="H51" s="83" t="s">
+      <c r="H51" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I51" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J51" s="83" t="s">
-        <v>397</v>
-      </c>
-      <c r="K51" s="83" t="s">
+      <c r="I51" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J51" s="73" t="s">
+        <v>396</v>
+      </c>
+      <c r="K51" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="L51" s="84">
-        <v>1</v>
-      </c>
-      <c r="M51" s="83">
+      <c r="L51" s="74">
+        <v>1</v>
+      </c>
+      <c r="M51" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N51" s="83">
+      <c r="N51" s="73">
         <v>100</v>
       </c>
-      <c r="O51" s="85" t="s">
+      <c r="O51" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P51" s="86">
+      <c r="P51" s="76">
         <v>1E-3</v>
       </c>
-      <c r="Q51" s="86">
+      <c r="Q51" s="76">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R51" s="87"/>
-      <c r="S51" s="87"/>
+      <c r="R51" s="77"/>
+      <c r="S51" s="77"/>
     </row>
     <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -5111,7 +5182,7 @@
         <v>355</v>
       </c>
       <c r="J52" s="46" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K52" s="46" t="s">
         <v>322</v>
@@ -5137,7 +5208,7 @@
         <v>0.16999999999999998</v>
       </c>
       <c r="R52" s="48"/>
-      <c r="S52" s="81"/>
+      <c r="S52" s="71"/>
     </row>
     <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -5145,45 +5216,55 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="82" t="s">
+      <c r="C53" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D53" s="83" t="s">
+      <c r="D53" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="E53" s="84" t="s">
+      <c r="E53" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="F53" s="83" t="s">
+      <c r="F53" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="G53" s="83" t="s">
+      <c r="G53" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="H53" s="83" t="s">
+      <c r="H53" s="73" t="s">
         <v>281</v>
       </c>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83" t="s">
+      <c r="I53" s="73" t="s">
+        <v>453</v>
+      </c>
+      <c r="J53" s="73" t="s">
+        <v>454</v>
+      </c>
+      <c r="K53" s="73" t="s">
         <v>323</v>
       </c>
-      <c r="L53" s="84">
-        <v>1</v>
-      </c>
-      <c r="M53" s="83">
+      <c r="L53" s="74">
+        <v>1</v>
+      </c>
+      <c r="M53" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N53" s="83"/>
-      <c r="O53" s="85"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="86">
+      <c r="N53" s="73">
+        <v>100</v>
+      </c>
+      <c r="O53" s="75" t="s">
+        <v>368</v>
+      </c>
+      <c r="P53" s="76">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q53" s="76">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R53" s="87"/>
-      <c r="S53" s="87"/>
+        <v>0.08</v>
+      </c>
+      <c r="R53" s="77"/>
+      <c r="S53" s="77"/>
     </row>
     <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -5213,7 +5294,7 @@
         <v>355</v>
       </c>
       <c r="J54" s="46" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K54" s="46" t="s">
         <v>324</v>
@@ -5232,14 +5313,14 @@
         <v>368</v>
       </c>
       <c r="P54" s="49">
-        <v>1.2999999999999999E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q54" s="49">
         <f t="shared" si="2"/>
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="R54" s="48"/>
-      <c r="S54" s="81"/>
+      <c r="S54" s="71"/>
     </row>
     <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
@@ -5247,55 +5328,55 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="82" t="s">
+      <c r="C55" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D55" s="83" t="s">
-        <v>447</v>
-      </c>
-      <c r="E55" s="84" t="s">
+      <c r="D55" s="73" t="s">
+        <v>444</v>
+      </c>
+      <c r="E55" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="F55" s="83" t="s">
+      <c r="F55" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="G55" s="83" t="s">
+      <c r="G55" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="H55" s="83" t="s">
+      <c r="H55" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I55" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J55" s="83" t="s">
-        <v>400</v>
-      </c>
-      <c r="K55" s="83" t="s">
+      <c r="I55" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J55" s="73" t="s">
+        <v>399</v>
+      </c>
+      <c r="K55" s="73" t="s">
         <v>325</v>
       </c>
-      <c r="L55" s="84">
-        <v>1</v>
-      </c>
-      <c r="M55" s="83">
+      <c r="L55" s="74">
+        <v>1</v>
+      </c>
+      <c r="M55" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N55" s="83">
+      <c r="N55" s="73">
         <v>100</v>
       </c>
-      <c r="O55" s="85" t="s">
+      <c r="O55" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P55" s="86">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q55" s="86">
+      <c r="P55" s="76">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q55" s="76">
         <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="R55" s="87"/>
-      <c r="S55" s="87"/>
+        <v>0.11</v>
+      </c>
+      <c r="R55" s="77"/>
+      <c r="S55" s="77"/>
     </row>
     <row r="56" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
@@ -5325,7 +5406,7 @@
         <v>355</v>
       </c>
       <c r="J56" s="46" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K56" s="46" t="s">
         <v>326</v>
@@ -5344,14 +5425,14 @@
         <v>368</v>
       </c>
       <c r="P56" s="49">
-        <v>3.0300000000000001E-2</v>
+        <v>3.0700000000000002E-2</v>
       </c>
       <c r="Q56" s="49">
         <f t="shared" si="2"/>
-        <v>0.60599999999999998</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="R56" s="48"/>
-      <c r="S56" s="81"/>
+      <c r="S56" s="71"/>
     </row>
     <row r="57" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
@@ -5359,55 +5440,55 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="82" t="s">
+      <c r="C57" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D57" s="83" t="s">
+      <c r="D57" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="84" t="s">
+      <c r="E57" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="F57" s="83" t="s">
+      <c r="F57" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="G57" s="83" t="s">
+      <c r="G57" s="73" t="s">
         <v>230</v>
       </c>
-      <c r="H57" s="83" t="s">
+      <c r="H57" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I57" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J57" s="83" t="s">
-        <v>402</v>
-      </c>
-      <c r="K57" s="83" t="s">
+      <c r="I57" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J57" s="73" t="s">
+        <v>401</v>
+      </c>
+      <c r="K57" s="73" t="s">
         <v>327</v>
       </c>
-      <c r="L57" s="84">
+      <c r="L57" s="74">
         <v>8</v>
       </c>
-      <c r="M57" s="83">
+      <c r="M57" s="73">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N57" s="83">
+      <c r="N57" s="73">
         <v>100</v>
       </c>
-      <c r="O57" s="85" t="s">
+      <c r="O57" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P57" s="86">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q57" s="86">
+      <c r="P57" s="76">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q57" s="76">
         <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="R57" s="87"/>
-      <c r="S57" s="87"/>
+        <v>0.11</v>
+      </c>
+      <c r="R57" s="77"/>
+      <c r="S57" s="77"/>
     </row>
     <row r="58" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
@@ -5437,7 +5518,7 @@
         <v>355</v>
       </c>
       <c r="J58" s="46" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K58" s="46" t="s">
         <v>328</v>
@@ -5456,14 +5537,14 @@
         <v>368</v>
       </c>
       <c r="P58" s="49">
-        <v>8.3900000000000002E-2</v>
+        <v>8.5699999999999998E-2</v>
       </c>
       <c r="Q58" s="49">
         <f t="shared" si="2"/>
-        <v>0.83899999999999997</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="R58" s="48"/>
-      <c r="S58" s="81"/>
+      <c r="S58" s="71"/>
     </row>
     <row r="59" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
@@ -5471,55 +5552,55 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="82" t="s">
+      <c r="C59" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D59" s="83" t="s">
+      <c r="D59" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="E59" s="84" t="s">
+      <c r="E59" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="F59" s="83" t="s">
+      <c r="F59" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="G59" s="83" t="s">
+      <c r="G59" s="73" t="s">
         <v>231</v>
       </c>
-      <c r="H59" s="83" t="s">
+      <c r="H59" s="73" t="s">
         <v>283</v>
       </c>
-      <c r="I59" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J59" s="83" t="s">
-        <v>404</v>
-      </c>
-      <c r="K59" s="83" t="s">
+      <c r="I59" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J59" s="73" t="s">
+        <v>403</v>
+      </c>
+      <c r="K59" s="73" t="s">
         <v>328</v>
       </c>
-      <c r="L59" s="84">
+      <c r="L59" s="74">
         <v>3</v>
       </c>
-      <c r="M59" s="83">
+      <c r="M59" s="73">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N59" s="83">
+      <c r="N59" s="73">
         <v>100</v>
       </c>
-      <c r="O59" s="85" t="s">
+      <c r="O59" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P59" s="86">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q59" s="86">
+      <c r="P59" s="76">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q59" s="76">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="R59" s="87"/>
-      <c r="S59" s="87"/>
+        <v>0.12</v>
+      </c>
+      <c r="R59" s="77"/>
+      <c r="S59" s="77"/>
     </row>
     <row r="60" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
@@ -5549,7 +5630,7 @@
         <v>355</v>
       </c>
       <c r="J60" s="46" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K60" s="46" t="s">
         <v>329</v>
@@ -5568,14 +5649,14 @@
         <v>368</v>
       </c>
       <c r="P60" s="49">
-        <v>6.4000000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="Q60" s="49">
         <f t="shared" si="2"/>
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="R60" s="48"/>
-      <c r="S60" s="81"/>
+      <c r="S60" s="71"/>
     </row>
     <row r="61" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
@@ -5583,55 +5664,55 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="82" t="s">
+      <c r="C61" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D61" s="83" t="s">
+      <c r="D61" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="E61" s="84" t="s">
+      <c r="E61" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="F61" s="83" t="s">
+      <c r="F61" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="G61" s="83" t="s">
+      <c r="G61" s="73" t="s">
         <v>233</v>
       </c>
-      <c r="H61" s="83" t="s">
+      <c r="H61" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I61" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J61" s="83" t="s">
-        <v>406</v>
-      </c>
-      <c r="K61" s="83" t="s">
+      <c r="I61" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J61" s="73" t="s">
+        <v>405</v>
+      </c>
+      <c r="K61" s="73" t="s">
         <v>330</v>
       </c>
-      <c r="L61" s="84">
+      <c r="L61" s="74">
         <v>4</v>
       </c>
-      <c r="M61" s="83">
+      <c r="M61" s="73">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="83">
+      <c r="N61" s="73">
         <v>100</v>
       </c>
-      <c r="O61" s="85" t="s">
+      <c r="O61" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P61" s="86">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q61" s="86">
+      <c r="P61" s="76">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q61" s="76">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="R61" s="87"/>
-      <c r="S61" s="87"/>
+        <v>0.12</v>
+      </c>
+      <c r="R61" s="77"/>
+      <c r="S61" s="77"/>
     </row>
     <row r="62" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
@@ -5661,7 +5742,7 @@
         <v>355</v>
       </c>
       <c r="J62" s="46" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K62" s="46" t="s">
         <v>331</v>
@@ -5680,14 +5761,14 @@
         <v>368</v>
       </c>
       <c r="P62" s="49">
-        <v>2.1499999999999998E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="Q62" s="49">
         <f t="shared" si="2"/>
-        <v>0.42999999999999994</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="R62" s="48"/>
-      <c r="S62" s="81"/>
+      <c r="S62" s="71"/>
     </row>
     <row r="63" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
@@ -5695,55 +5776,55 @@
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="82" t="s">
+      <c r="C63" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D63" s="83" t="s">
+      <c r="D63" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="E63" s="84" t="s">
+      <c r="E63" s="74" t="s">
         <v>131</v>
       </c>
-      <c r="F63" s="83" t="s">
+      <c r="F63" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="G63" s="83" t="s">
+      <c r="G63" s="73" t="s">
+        <v>407</v>
+      </c>
+      <c r="H63" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="I63" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J63" s="73" t="s">
         <v>408</v>
       </c>
-      <c r="H63" s="83" t="s">
-        <v>286</v>
-      </c>
-      <c r="I63" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J63" s="83" t="s">
-        <v>409</v>
-      </c>
-      <c r="K63" s="83" t="s">
+      <c r="K63" s="73" t="s">
         <v>332</v>
       </c>
-      <c r="L63" s="84">
-        <v>1</v>
-      </c>
-      <c r="M63" s="83">
+      <c r="L63" s="74">
+        <v>1</v>
+      </c>
+      <c r="M63" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N63" s="83">
-        <v>50</v>
-      </c>
-      <c r="O63" s="85" t="s">
+      <c r="N63" s="73">
+        <v>100</v>
+      </c>
+      <c r="O63" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P63" s="86">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="Q63" s="86">
+      <c r="P63" s="76">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q63" s="76">
         <f t="shared" si="2"/>
-        <v>0.20500000000000002</v>
-      </c>
-      <c r="R63" s="87"/>
-      <c r="S63" s="87"/>
+        <v>0.38</v>
+      </c>
+      <c r="R63" s="77"/>
+      <c r="S63" s="77"/>
     </row>
     <row r="64" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
@@ -5773,7 +5854,7 @@
         <v>355</v>
       </c>
       <c r="J64" s="46" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K64" s="46" t="s">
         <v>333</v>
@@ -5792,14 +5873,14 @@
         <v>368</v>
       </c>
       <c r="P64" s="49">
-        <v>1.9E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q64" s="49">
         <f t="shared" si="2"/>
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="R64" s="48"/>
-      <c r="S64" s="81"/>
+      <c r="S64" s="71"/>
     </row>
     <row r="65" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
@@ -5807,55 +5888,55 @@
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="82" t="s">
+      <c r="C65" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D65" s="83" t="s">
+      <c r="D65" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="E65" s="84" t="s">
+      <c r="E65" s="74" t="s">
         <v>133</v>
       </c>
-      <c r="F65" s="83" t="s">
+      <c r="F65" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="G65" s="83" t="s">
+      <c r="G65" s="73" t="s">
         <v>237</v>
       </c>
-      <c r="H65" s="83" t="s">
+      <c r="H65" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I65" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J65" s="83" t="s">
-        <v>412</v>
-      </c>
-      <c r="K65" s="83" t="s">
+      <c r="I65" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J65" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="K65" s="73" t="s">
         <v>334</v>
       </c>
-      <c r="L65" s="84">
+      <c r="L65" s="74">
         <v>2</v>
       </c>
-      <c r="M65" s="83">
+      <c r="M65" s="73">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N65" s="83">
+      <c r="N65" s="73">
         <v>100</v>
       </c>
-      <c r="O65" s="85" t="s">
+      <c r="O65" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P65" s="86">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q65" s="86">
+      <c r="P65" s="76">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q65" s="76">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="R65" s="87"/>
-      <c r="S65" s="87"/>
+        <v>0.12</v>
+      </c>
+      <c r="R65" s="77"/>
+      <c r="S65" s="77"/>
     </row>
     <row r="66" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
@@ -5875,17 +5956,17 @@
       <c r="F66" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="G66" s="47" t="s">
+      <c r="G66" s="59" t="s">
         <v>238</v>
       </c>
       <c r="H66" s="46" t="s">
         <v>255</v>
       </c>
       <c r="I66" s="46" t="s">
-        <v>355</v>
+        <v>455</v>
       </c>
       <c r="J66" s="46" t="s">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="K66" s="46" t="s">
         <v>335</v>
@@ -5898,20 +5979,20 @@
         <v>5</v>
       </c>
       <c r="N66" s="46">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O66" s="58" t="s">
         <v>368</v>
       </c>
       <c r="P66" s="49">
-        <v>3.8199999999999998E-2</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q66" s="49">
         <f t="shared" si="2"/>
-        <v>0.76400000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="R66" s="48"/>
-      <c r="S66" s="81"/>
+      <c r="S66" s="71"/>
     </row>
     <row r="67" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
@@ -5919,55 +6000,55 @@
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="82" t="s">
+      <c r="C67" s="72" t="s">
         <v>284</v>
       </c>
-      <c r="D67" s="83" t="s">
+      <c r="D67" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="E67" s="84" t="s">
+      <c r="E67" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="F67" s="83" t="s">
+      <c r="F67" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="G67" s="83" t="s">
+      <c r="G67" s="73" t="s">
         <v>239</v>
       </c>
-      <c r="H67" s="83" t="s">
+      <c r="H67" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="I67" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J67" s="83" t="s">
-        <v>413</v>
-      </c>
-      <c r="K67" s="83" t="s">
+      <c r="I67" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J67" s="73" t="s">
+        <v>411</v>
+      </c>
+      <c r="K67" s="73" t="s">
         <v>336</v>
       </c>
-      <c r="L67" s="84">
-        <v>1</v>
-      </c>
-      <c r="M67" s="83">
+      <c r="L67" s="74">
+        <v>1</v>
+      </c>
+      <c r="M67" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N67" s="83">
+      <c r="N67" s="73">
         <v>100</v>
       </c>
-      <c r="O67" s="85" t="s">
+      <c r="O67" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P67" s="86">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q67" s="86">
+      <c r="P67" s="76">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q67" s="76">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R67" s="87"/>
-      <c r="S67" s="87"/>
+        <v>0.12</v>
+      </c>
+      <c r="R67" s="77"/>
+      <c r="S67" s="77"/>
     </row>
     <row r="68" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -5997,7 +6078,7 @@
         <v>355</v>
       </c>
       <c r="J68" s="46" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K68" s="46" t="s">
         <v>355</v>
@@ -6016,14 +6097,14 @@
         <v>368</v>
       </c>
       <c r="P68" s="49">
-        <v>0.1487</v>
+        <v>0.1376</v>
       </c>
       <c r="Q68" s="49">
         <f t="shared" si="2"/>
-        <v>1.4870000000000001</v>
+        <v>1.3759999999999999</v>
       </c>
       <c r="R68" s="48"/>
-      <c r="S68" s="81"/>
+      <c r="S68" s="71"/>
     </row>
     <row r="69" spans="1:19" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -6031,54 +6112,54 @@
         <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="82" t="s">
+      <c r="C69" s="93" t="s">
         <v>182</v>
       </c>
-      <c r="D69" s="83" t="s">
+      <c r="D69" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="E69" s="84" t="s">
+      <c r="E69" s="94" t="s">
         <v>137</v>
       </c>
-      <c r="F69" s="83" t="s">
+      <c r="F69" s="78" t="s">
         <v>354</v>
       </c>
-      <c r="G69" s="83" t="s">
+      <c r="G69" s="78" t="s">
         <v>182</v>
       </c>
-      <c r="H69" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="I69" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J69" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="K69" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L69" s="84">
+      <c r="H69" s="78" t="s">
+        <v>355</v>
+      </c>
+      <c r="I69" s="78" t="s">
+        <v>355</v>
+      </c>
+      <c r="J69" s="78" t="s">
+        <v>355</v>
+      </c>
+      <c r="K69" s="78" t="s">
+        <v>355</v>
+      </c>
+      <c r="L69" s="94">
         <v>38</v>
       </c>
-      <c r="M69" s="83">
+      <c r="M69" s="78">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="N69" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="O69" s="85" t="s">
-        <v>355</v>
-      </c>
-      <c r="P69" s="86" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q69" s="86" t="s">
-        <v>355</v>
-      </c>
-      <c r="R69" s="87"/>
-      <c r="S69" s="87"/>
+      <c r="N69" s="78" t="s">
+        <v>355</v>
+      </c>
+      <c r="O69" s="95" t="s">
+        <v>355</v>
+      </c>
+      <c r="P69" s="96" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q69" s="96" t="s">
+        <v>355</v>
+      </c>
+      <c r="R69" s="97"/>
+      <c r="S69" s="97"/>
     </row>
     <row r="70" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
@@ -6108,7 +6189,7 @@
         <v>355</v>
       </c>
       <c r="J70" s="46" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K70" s="46" t="s">
         <v>355</v>
@@ -6134,7 +6215,7 @@
         <v>1.26</v>
       </c>
       <c r="R70" s="48"/>
-      <c r="S70" s="81"/>
+      <c r="S70" s="71"/>
     </row>
     <row r="71" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
@@ -6142,55 +6223,55 @@
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="82" t="s">
+      <c r="C71" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="D71" s="83" t="s">
+      <c r="D71" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="E71" s="84" t="s">
+      <c r="E71" s="74" t="s">
         <v>139</v>
       </c>
-      <c r="F71" s="83" t="s">
+      <c r="F71" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="G71" s="83" t="s">
+      <c r="G71" s="78" t="s">
         <v>240</v>
       </c>
-      <c r="H71" s="83" t="s">
+      <c r="H71" s="73" t="s">
         <v>277</v>
       </c>
-      <c r="I71" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J71" s="83" t="s">
-        <v>416</v>
-      </c>
-      <c r="K71" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L71" s="84">
-        <v>1</v>
-      </c>
-      <c r="M71" s="83">
+      <c r="I71" s="73" t="s">
+        <v>457</v>
+      </c>
+      <c r="J71" s="73" t="s">
+        <v>458</v>
+      </c>
+      <c r="K71" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L71" s="74">
+        <v>1</v>
+      </c>
+      <c r="M71" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N71" s="83">
+      <c r="N71" s="73">
         <v>6</v>
       </c>
-      <c r="O71" s="85" t="s">
+      <c r="O71" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P71" s="86">
-        <v>0.49059999999999998</v>
-      </c>
-      <c r="Q71" s="86">
+      <c r="P71" s="76">
+        <v>0.39939999999999998</v>
+      </c>
+      <c r="Q71" s="76">
         <f t="shared" si="2"/>
-        <v>2.9436</v>
-      </c>
-      <c r="R71" s="87"/>
-      <c r="S71" s="87"/>
+        <v>2.3963999999999999</v>
+      </c>
+      <c r="R71" s="77"/>
+      <c r="S71" s="77"/>
     </row>
     <row r="72" spans="1:19" s="70" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="62"/>
@@ -6236,19 +6317,19 @@
         <v>6</v>
       </c>
       <c r="O72" s="67" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="P72" s="68">
-        <v>10.87</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="Q72" s="68">
         <f t="shared" ref="Q72:Q84" si="4">P72*N72</f>
-        <v>65.22</v>
+        <v>52.800000000000004</v>
       </c>
       <c r="R72" s="69" t="s">
-        <v>452</v>
-      </c>
-      <c r="S72" s="81"/>
+        <v>449</v>
+      </c>
+      <c r="S72" s="71"/>
     </row>
     <row r="73" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
@@ -6256,55 +6337,55 @@
         <f>ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
-      <c r="C73" s="82" t="s">
+      <c r="C73" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="D73" s="83" t="s">
+      <c r="D73" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="E73" s="84" t="s">
+      <c r="E73" s="74" t="s">
         <v>141</v>
       </c>
-      <c r="F73" s="83" t="s">
+      <c r="F73" s="73" t="s">
         <v>186</v>
       </c>
-      <c r="G73" s="83" t="s">
+      <c r="G73" s="73" t="s">
         <v>242</v>
       </c>
-      <c r="H73" s="83" t="s">
+      <c r="H73" s="73" t="s">
         <v>278</v>
       </c>
-      <c r="I73" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J73" s="83" t="s">
-        <v>417</v>
-      </c>
-      <c r="K73" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L73" s="84">
+      <c r="I73" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J73" s="73" t="s">
+        <v>414</v>
+      </c>
+      <c r="K73" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L73" s="74">
         <v>2</v>
       </c>
-      <c r="M73" s="83">
+      <c r="M73" s="73">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N73" s="83">
+      <c r="N73" s="73">
         <v>11</v>
       </c>
-      <c r="O73" s="85" t="s">
+      <c r="O73" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P73" s="86">
-        <v>0.79530000000000001</v>
-      </c>
-      <c r="Q73" s="86">
+      <c r="P73" s="76">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="Q73" s="76">
         <f t="shared" si="4"/>
-        <v>8.7483000000000004</v>
-      </c>
-      <c r="R73" s="87"/>
-      <c r="S73" s="87"/>
+        <v>6.5285000000000002</v>
+      </c>
+      <c r="R73" s="77"/>
+      <c r="S73" s="77"/>
     </row>
     <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -6334,7 +6415,7 @@
         <v>355</v>
       </c>
       <c r="J74" s="46" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="K74" s="46" t="s">
         <v>355</v>
@@ -6347,20 +6428,20 @@
         <v>5</v>
       </c>
       <c r="N74" s="46">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O74" s="58" t="s">
         <v>368</v>
       </c>
       <c r="P74" s="49">
-        <v>0.38390000000000002</v>
+        <v>0.30840000000000001</v>
       </c>
       <c r="Q74" s="49">
         <f t="shared" si="4"/>
-        <v>2.3033999999999999</v>
+        <v>3.0840000000000001</v>
       </c>
       <c r="R74" s="48"/>
-      <c r="S74" s="81"/>
+      <c r="S74" s="71"/>
     </row>
     <row r="75" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
@@ -6368,55 +6449,55 @@
         <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="82" t="s">
+      <c r="C75" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="D75" s="83" t="s">
+      <c r="D75" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="E75" s="84" t="s">
+      <c r="E75" s="74" t="s">
         <v>143</v>
       </c>
-      <c r="F75" s="83" t="s">
+      <c r="F75" s="73" t="s">
         <v>186</v>
       </c>
-      <c r="G75" s="83" t="s">
+      <c r="G75" s="73" t="s">
         <v>244</v>
       </c>
-      <c r="H75" s="83" t="s">
+      <c r="H75" s="73" t="s">
         <v>290</v>
       </c>
-      <c r="I75" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J75" s="83" t="s">
-        <v>418</v>
-      </c>
-      <c r="K75" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L75" s="84">
-        <v>1</v>
-      </c>
-      <c r="M75" s="83">
+      <c r="I75" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J75" s="73" t="s">
+        <v>415</v>
+      </c>
+      <c r="K75" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L75" s="74">
+        <v>1</v>
+      </c>
+      <c r="M75" s="73">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N75" s="83">
+      <c r="N75" s="73">
         <v>6</v>
       </c>
-      <c r="O75" s="85" t="s">
+      <c r="O75" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P75" s="86">
-        <v>2.5665</v>
-      </c>
-      <c r="Q75" s="86">
+      <c r="P75" s="76">
+        <v>2.2416</v>
+      </c>
+      <c r="Q75" s="76">
         <f t="shared" si="4"/>
-        <v>15.399000000000001</v>
-      </c>
-      <c r="R75" s="87"/>
-      <c r="S75" s="87"/>
+        <v>13.4496</v>
+      </c>
+      <c r="R75" s="77"/>
+      <c r="S75" s="77"/>
     </row>
     <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
@@ -6462,19 +6543,19 @@
         <v>6</v>
       </c>
       <c r="O76" s="58" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="P76" s="49">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="Q76" s="49">
         <f t="shared" si="4"/>
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="R76" s="69" t="s">
-        <v>452</v>
-      </c>
-      <c r="S76" s="81"/>
+        <v>449</v>
+      </c>
+      <c r="S76" s="71"/>
     </row>
     <row r="77" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
@@ -6482,55 +6563,55 @@
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="82" t="s">
+      <c r="C77" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="D77" s="83" t="s">
+      <c r="D77" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="E77" s="84" t="s">
+      <c r="E77" s="74" t="s">
         <v>145</v>
       </c>
-      <c r="F77" s="83" t="s">
+      <c r="F77" s="73" t="s">
         <v>188</v>
       </c>
-      <c r="G77" s="83" t="s">
+      <c r="G77" s="73" t="s">
         <v>246</v>
       </c>
-      <c r="H77" s="83" t="s">
+      <c r="H77" s="73" t="s">
         <v>292</v>
       </c>
-      <c r="I77" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J77" s="83" t="s">
-        <v>420</v>
-      </c>
-      <c r="K77" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L77" s="84">
-        <v>1</v>
-      </c>
-      <c r="M77" s="83">
+      <c r="I77" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J77" s="73" t="s">
+        <v>417</v>
+      </c>
+      <c r="K77" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L77" s="74">
+        <v>1</v>
+      </c>
+      <c r="M77" s="73">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N77" s="83">
+      <c r="N77" s="73">
         <v>6</v>
       </c>
-      <c r="O77" s="85" t="s">
+      <c r="O77" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P77" s="86">
-        <v>0.76259999999999994</v>
-      </c>
-      <c r="Q77" s="86">
+      <c r="P77" s="76">
+        <v>0.76690000000000003</v>
+      </c>
+      <c r="Q77" s="76">
         <f t="shared" si="4"/>
-        <v>4.5755999999999997</v>
-      </c>
-      <c r="R77" s="87"/>
-      <c r="S77" s="87"/>
+        <v>4.6013999999999999</v>
+      </c>
+      <c r="R77" s="77"/>
+      <c r="S77" s="77"/>
     </row>
     <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -6560,7 +6641,7 @@
         <v>355</v>
       </c>
       <c r="J78" s="46" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K78" s="46" t="s">
         <v>355</v>
@@ -6586,7 +6667,7 @@
         <v>25.2624</v>
       </c>
       <c r="R78" s="48"/>
-      <c r="S78" s="81"/>
+      <c r="S78" s="71"/>
     </row>
     <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -6594,55 +6675,55 @@
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="82" t="s">
+      <c r="C79" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="D79" s="83" t="s">
+      <c r="D79" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="E79" s="84" t="s">
+      <c r="E79" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="F79" s="83" t="s">
+      <c r="F79" s="73" t="s">
         <v>354</v>
       </c>
-      <c r="G79" s="83" t="s">
+      <c r="G79" s="73" t="s">
         <v>190</v>
       </c>
-      <c r="H79" s="83" t="s">
+      <c r="H79" s="73" t="s">
         <v>294</v>
       </c>
-      <c r="I79" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J79" s="83" t="s">
-        <v>422</v>
-      </c>
-      <c r="K79" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L79" s="84">
-        <v>1</v>
-      </c>
-      <c r="M79" s="83">
+      <c r="I79" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J79" s="73" t="s">
+        <v>419</v>
+      </c>
+      <c r="K79" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L79" s="74">
+        <v>1</v>
+      </c>
+      <c r="M79" s="73">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N79" s="83">
+      <c r="N79" s="73">
         <v>6</v>
       </c>
-      <c r="O79" s="85" t="s">
+      <c r="O79" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P79" s="86">
-        <v>1.4825999999999999</v>
-      </c>
-      <c r="Q79" s="86">
+      <c r="P79" s="76">
+        <v>1.4591000000000001</v>
+      </c>
+      <c r="Q79" s="76">
         <f t="shared" si="4"/>
-        <v>8.8956</v>
-      </c>
-      <c r="R79" s="87"/>
-      <c r="S79" s="87"/>
+        <v>8.7545999999999999</v>
+      </c>
+      <c r="R79" s="77"/>
+      <c r="S79" s="77"/>
     </row>
     <row r="80" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
@@ -6688,19 +6769,19 @@
         <v>6</v>
       </c>
       <c r="O80" s="58" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="P80" s="49">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q80" s="49">
         <f t="shared" si="4"/>
-        <v>19.200000000000003</v>
+        <v>22.200000000000003</v>
       </c>
       <c r="R80" s="69" t="s">
-        <v>452</v>
-      </c>
-      <c r="S80" s="81"/>
+        <v>449</v>
+      </c>
+      <c r="S80" s="71"/>
     </row>
     <row r="81" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
@@ -6708,55 +6789,55 @@
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="82" t="s">
+      <c r="C81" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="D81" s="83" t="s">
+      <c r="D81" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="E81" s="84" t="s">
+      <c r="E81" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="F81" s="83" t="s">
+      <c r="F81" s="73" t="s">
         <v>191</v>
       </c>
-      <c r="G81" s="83" t="s">
+      <c r="G81" s="73" t="s">
         <v>249</v>
       </c>
-      <c r="H81" s="83" t="s">
+      <c r="H81" s="73" t="s">
         <v>295</v>
       </c>
-      <c r="I81" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J81" s="83" t="s">
-        <v>423</v>
-      </c>
-      <c r="K81" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="L81" s="84">
-        <v>1</v>
-      </c>
-      <c r="M81" s="83">
+      <c r="I81" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J81" s="73" t="s">
+        <v>420</v>
+      </c>
+      <c r="K81" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="L81" s="74">
+        <v>1</v>
+      </c>
+      <c r="M81" s="73">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N81" s="83">
+      <c r="N81" s="73">
         <v>6</v>
       </c>
-      <c r="O81" s="85" t="s">
+      <c r="O81" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P81" s="86">
-        <v>0.49230000000000002</v>
-      </c>
-      <c r="Q81" s="86">
+      <c r="P81" s="76">
+        <v>0.47570000000000001</v>
+      </c>
+      <c r="Q81" s="76">
         <f t="shared" si="4"/>
-        <v>2.9538000000000002</v>
-      </c>
-      <c r="R81" s="87"/>
-      <c r="S81" s="87"/>
+        <v>2.8542000000000001</v>
+      </c>
+      <c r="R81" s="77"/>
+      <c r="S81" s="77"/>
     </row>
     <row r="82" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
@@ -6802,19 +6883,19 @@
         <v>6</v>
       </c>
       <c r="O82" s="58" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="P82" s="49">
-        <v>1.45</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Q82" s="49">
         <f t="shared" si="4"/>
-        <v>8.6999999999999993</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="R82" s="69" t="s">
-        <v>452</v>
-      </c>
-      <c r="S82" s="81"/>
+        <v>449</v>
+      </c>
+      <c r="S82" s="71"/>
     </row>
     <row r="83" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
@@ -6822,55 +6903,55 @@
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="82" t="s">
+      <c r="C83" s="72" t="s">
         <v>353</v>
       </c>
-      <c r="D83" s="83" t="s">
+      <c r="D83" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="E83" s="84" t="s">
+      <c r="E83" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="F83" s="83" t="s">
+      <c r="F83" s="73" t="s">
         <v>354</v>
       </c>
-      <c r="G83" s="83" t="s">
+      <c r="G83" s="73" t="s">
         <v>192</v>
       </c>
-      <c r="H83" s="83" t="s">
+      <c r="H83" s="73" t="s">
         <v>297</v>
       </c>
-      <c r="I83" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="J83" s="83" t="s">
-        <v>424</v>
-      </c>
-      <c r="K83" s="83" t="s">
+      <c r="I83" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="J83" s="73" t="s">
+        <v>421</v>
+      </c>
+      <c r="K83" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="L83" s="84">
-        <v>1</v>
-      </c>
-      <c r="M83" s="83">
+      <c r="L83" s="74">
+        <v>1</v>
+      </c>
+      <c r="M83" s="73">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N83" s="83">
+      <c r="N83" s="73">
         <v>10</v>
       </c>
-      <c r="O83" s="85" t="s">
+      <c r="O83" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="P83" s="86">
-        <v>8.6900000000000005E-2</v>
-      </c>
-      <c r="Q83" s="86">
+      <c r="P83" s="76">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="Q83" s="76">
         <f t="shared" si="4"/>
-        <v>0.86899999999999999</v>
-      </c>
-      <c r="R83" s="87"/>
-      <c r="S83" s="87"/>
+        <v>0.85999999999999988</v>
+      </c>
+      <c r="R83" s="77"/>
+      <c r="S83" s="77"/>
     </row>
     <row r="84" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
@@ -6900,7 +6981,7 @@
         <v>355</v>
       </c>
       <c r="J84" s="46" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="K84" s="46" t="s">
         <v>338</v>
@@ -6919,14 +7000,14 @@
         <v>368</v>
       </c>
       <c r="P84" s="49">
-        <v>0.112</v>
+        <v>0.1221</v>
       </c>
       <c r="Q84" s="49">
         <f t="shared" si="4"/>
-        <v>1.1200000000000001</v>
+        <v>1.2210000000000001</v>
       </c>
       <c r="R84" s="48"/>
-      <c r="S84" s="81"/>
+      <c r="S84" s="71"/>
     </row>
     <row r="85" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
@@ -6942,17 +7023,17 @@
       <c r="K85" s="37"/>
       <c r="L85" s="37"/>
       <c r="M85" s="37"/>
-      <c r="N85" s="79" t="s">
-        <v>448</v>
-      </c>
-      <c r="O85" s="80"/>
-      <c r="P85" s="80"/>
+      <c r="N85" s="87" t="s">
+        <v>445</v>
+      </c>
+      <c r="O85" s="88"/>
+      <c r="P85" s="88"/>
       <c r="Q85" s="60">
         <f>SUM(Q10:Q84)</f>
-        <v>510.77860000000004</v>
-      </c>
-      <c r="R85" s="75"/>
-      <c r="S85" s="76"/>
+        <v>477.95680000000004</v>
+      </c>
+      <c r="R85" s="83"/>
+      <c r="S85" s="84"/>
     </row>
     <row r="86" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
@@ -6968,17 +7049,17 @@
       <c r="K86" s="10"/>
       <c r="L86" s="10"/>
       <c r="M86" s="10"/>
-      <c r="N86" s="79" t="s">
-        <v>449</v>
-      </c>
-      <c r="O86" s="80"/>
-      <c r="P86" s="80"/>
+      <c r="N86" s="87" t="s">
+        <v>446</v>
+      </c>
+      <c r="O86" s="88"/>
+      <c r="P86" s="88"/>
       <c r="Q86" s="61">
         <f>Q85/5</f>
-        <v>102.15572</v>
-      </c>
-      <c r="R86" s="77"/>
-      <c r="S86" s="78"/>
+        <v>95.591360000000009</v>
+      </c>
+      <c r="R86" s="85"/>
+      <c r="S86" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7031,36 +7112,37 @@
     <hyperlink ref="O63" r:id="rId40"/>
     <hyperlink ref="O64" r:id="rId41"/>
     <hyperlink ref="O65" r:id="rId42"/>
-    <hyperlink ref="O66" r:id="rId43"/>
-    <hyperlink ref="O67" r:id="rId44"/>
-    <hyperlink ref="O68" r:id="rId45"/>
-    <hyperlink ref="O70" r:id="rId46"/>
-    <hyperlink ref="O71" r:id="rId47"/>
-    <hyperlink ref="O73" r:id="rId48"/>
-    <hyperlink ref="O75" r:id="rId49"/>
-    <hyperlink ref="O74" r:id="rId50"/>
-    <hyperlink ref="O77" r:id="rId51"/>
-    <hyperlink ref="O78" r:id="rId52"/>
-    <hyperlink ref="O79" r:id="rId53"/>
-    <hyperlink ref="O81" r:id="rId54"/>
-    <hyperlink ref="O83" r:id="rId55"/>
-    <hyperlink ref="O84" r:id="rId56"/>
-    <hyperlink ref="O22" r:id="rId57"/>
-    <hyperlink ref="O24" r:id="rId58"/>
-    <hyperlink ref="O26" r:id="rId59"/>
-    <hyperlink ref="O27" r:id="rId60"/>
-    <hyperlink ref="O28" r:id="rId61"/>
-    <hyperlink ref="O29" r:id="rId62"/>
-    <hyperlink ref="O31" r:id="rId63"/>
-    <hyperlink ref="O32" r:id="rId64"/>
-    <hyperlink ref="O39" r:id="rId65"/>
-    <hyperlink ref="O38" r:id="rId66"/>
-    <hyperlink ref="O41" r:id="rId67"/>
-    <hyperlink ref="O43" r:id="rId68"/>
+    <hyperlink ref="O67" r:id="rId43"/>
+    <hyperlink ref="O68" r:id="rId44"/>
+    <hyperlink ref="O70" r:id="rId45"/>
+    <hyperlink ref="O73" r:id="rId46"/>
+    <hyperlink ref="O75" r:id="rId47"/>
+    <hyperlink ref="O74" r:id="rId48"/>
+    <hyperlink ref="O77" r:id="rId49"/>
+    <hyperlink ref="O78" r:id="rId50"/>
+    <hyperlink ref="O79" r:id="rId51"/>
+    <hyperlink ref="O81" r:id="rId52"/>
+    <hyperlink ref="O83" r:id="rId53"/>
+    <hyperlink ref="O84" r:id="rId54"/>
+    <hyperlink ref="O22" r:id="rId55"/>
+    <hyperlink ref="O24" r:id="rId56"/>
+    <hyperlink ref="O26" r:id="rId57"/>
+    <hyperlink ref="O27" r:id="rId58"/>
+    <hyperlink ref="O28" r:id="rId59"/>
+    <hyperlink ref="O29" r:id="rId60"/>
+    <hyperlink ref="O31" r:id="rId61"/>
+    <hyperlink ref="O32" r:id="rId62"/>
+    <hyperlink ref="O39" r:id="rId63"/>
+    <hyperlink ref="O38" r:id="rId64"/>
+    <hyperlink ref="O41" r:id="rId65"/>
+    <hyperlink ref="O43" r:id="rId66"/>
+    <hyperlink ref="O53" r:id="rId67"/>
+    <hyperlink ref="O66" r:id="rId68"/>
+    <hyperlink ref="O71" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId69"/>
-  <drawing r:id="rId70"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId70"/>
+  <drawing r:id="rId71"/>
 </worksheet>
 </file>
 
